--- a/Hotel-Brendle-Loan-Application.xlsx
+++ b/Hotel-Brendle-Loan-Application.xlsx
@@ -75,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -92,6 +92,8 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -457,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,155 +530,345 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Currently Occupied:</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>To Be Renovated:</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B10" t="n">
         <v>43</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Renovation Timeline:</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>6 months</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>LOAN REQUEST</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Amount Requested:</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B14" s="3" t="n">
         <v>850000</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>USE OF PROCEEDS</t>
         </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Existing Debt Payoff</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Amenities &amp; Jobsite Costs</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>100000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Room Renovation (40 rooms @ $15k)</t>
+          <t>Existing Debt Payoff</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>600000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Renovation &amp; Amenities (43 rooms)</t>
+        </is>
+      </c>
+      <c r="B18" s="5">
+        <f>'Sources &amp; Uses'!B9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Contingency</t>
+        </is>
+      </c>
+      <c r="B19" s="5">
+        <f>'Sources &amp; Uses'!B10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Total Uses</t>
         </is>
       </c>
-      <c r="B18" s="3">
-        <f>SUM(B15:B17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="B20" s="3">
+        <f>'Sources &amp; Uses'!B11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>LOAN TERMS</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Interest Rate:</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n">
-        <v>0.075</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Amortization:</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>25 years</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Monthly Payment (P&amp;I):</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="n">
-        <v>6281.43</v>
+          <t>Interest Rate:</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>0.075</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Amortization:</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>25 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Monthly Payment (P&amp;I):</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>6281.43</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Annual Debt Service:</t>
         </is>
       </c>
-      <c r="B24" s="5">
-        <f>B23*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>KEY METRICS (Year 3 Stabilized)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="B26" s="5">
+        <f>B$B25*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>CURRENT OPERATIONS (April 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Occupied Rooms:</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Monthly Revenue:</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>15340</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Annual NOI:</t>
+        </is>
+      </c>
+      <c r="B31" s="5">
+        <f>'Current Operations'!B25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>STABILIZED PROJECTIONS (Year 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Stabilized Occupancy:</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Stabilized Occupied Rooms:</t>
+        </is>
+      </c>
+      <c r="B35" s="15">
+        <f>67*B$34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Annual Gross Revenue:</t>
+        </is>
+      </c>
+      <c r="B36" s="5">
+        <f>'Annual Summary'!B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Annual Operating Expenses:</t>
+        </is>
+      </c>
+      <c r="B37" s="5">
+        <f>'Annual Summary'!C6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Stabilized NOI:</t>
         </is>
       </c>
-      <c r="B27" s="5">
+      <c r="B38" s="3">
         <f>'Annual Summary'!D6</f>
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>DSCR:</t>
         </is>
       </c>
-      <c r="B28" s="8">
+      <c r="B39" s="17">
         <f>'Annual Summary'!G6</f>
         <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>PROPERTY VALUATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Stabilized Value (Year 3, 10% cap):</t>
+        </is>
+      </c>
+      <c r="B42" s="5">
+        <f>'Property Valuation'!B11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Loan Amount:</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>850000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Loan-to-Value (LTV):</t>
+        </is>
+      </c>
+      <c r="B44" s="10">
+        <f>'Property Valuation'!B16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Owner Equity:</t>
+        </is>
+      </c>
+      <c r="B45" s="5">
+        <f>'Property Valuation'!B17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>REVENUE SOURCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Room Rental Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Laundry Revenue (6 washers, 6 dryers)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 1.0 load per occupied room per week</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - $4.50 per load (wash + dry)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3651,7 +3843,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -3680,7 +3871,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Room Revenue</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -3695,20 +3886,25 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
+          <t>Op Expenses</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
           <t>NOI</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>Debt Svc</t>
-        </is>
-      </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
+          <t>Debt Service</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
           <t>Cash Flow</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>DSCR</t>
         </is>
@@ -3743,16 +3939,15 @@
         <v/>
       </c>
       <c r="I4" s="5">
-        <f>F4-G4</f>
+        <f>C4*344</f>
         <v/>
       </c>
       <c r="J4" s="5">
         <f>H4-I4</f>
         <v/>
       </c>
-      <c r="K4" s="5">
-        <f>H4-I4</f>
-        <v/>
+      <c r="K4" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L4" s="5">
         <f>J4-K4</f>
@@ -3792,16 +3987,15 @@
         <v/>
       </c>
       <c r="I5" s="5">
-        <f>F5-G5</f>
+        <f>C5*344</f>
         <v/>
       </c>
       <c r="J5" s="5">
         <f>H5-I5</f>
         <v/>
       </c>
-      <c r="K5" s="5">
-        <f>H5-I5</f>
-        <v/>
+      <c r="K5" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L5" s="5">
         <f>J5-K5</f>
@@ -3841,16 +4035,15 @@
         <v/>
       </c>
       <c r="I6" s="5">
-        <f>F6-G6</f>
+        <f>C6*344</f>
         <v/>
       </c>
       <c r="J6" s="5">
         <f>H6-I6</f>
         <v/>
       </c>
-      <c r="K6" s="5">
-        <f>H6-I6</f>
-        <v/>
+      <c r="K6" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L6" s="5">
         <f>J6-K6</f>
@@ -3890,16 +4083,15 @@
         <v/>
       </c>
       <c r="I7" s="5">
-        <f>F7-G7</f>
+        <f>C7*344</f>
         <v/>
       </c>
       <c r="J7" s="5">
         <f>H7-I7</f>
         <v/>
       </c>
-      <c r="K7" s="5">
-        <f>H7-I7</f>
-        <v/>
+      <c r="K7" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L7" s="5">
         <f>J7-K7</f>
@@ -3939,16 +4131,15 @@
         <v/>
       </c>
       <c r="I8" s="5">
-        <f>F8-G8</f>
+        <f>C8*344</f>
         <v/>
       </c>
       <c r="J8" s="5">
         <f>H8-I8</f>
         <v/>
       </c>
-      <c r="K8" s="5">
-        <f>H8-I8</f>
-        <v/>
+      <c r="K8" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L8" s="5">
         <f>J8-K8</f>
@@ -3988,16 +4179,15 @@
         <v/>
       </c>
       <c r="I9" s="5">
-        <f>F9-G9</f>
+        <f>C9*344</f>
         <v/>
       </c>
       <c r="J9" s="5">
         <f>H9-I9</f>
         <v/>
       </c>
-      <c r="K9" s="5">
-        <f>H9-I9</f>
-        <v/>
+      <c r="K9" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L9" s="5">
         <f>J9-K9</f>
@@ -4037,16 +4227,15 @@
         <v/>
       </c>
       <c r="I10" s="5">
-        <f>F10-G10</f>
+        <f>C10*344</f>
         <v/>
       </c>
       <c r="J10" s="5">
         <f>H10-I10</f>
         <v/>
       </c>
-      <c r="K10" s="5">
-        <f>H10-I10</f>
-        <v/>
+      <c r="K10" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L10" s="5">
         <f>J10-K10</f>
@@ -4086,16 +4275,15 @@
         <v/>
       </c>
       <c r="I11" s="5">
-        <f>F11-G11</f>
+        <f>C11*344</f>
         <v/>
       </c>
       <c r="J11" s="5">
         <f>H11-I11</f>
         <v/>
       </c>
-      <c r="K11" s="5">
-        <f>H11-I11</f>
-        <v/>
+      <c r="K11" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L11" s="5">
         <f>J11-K11</f>
@@ -4135,16 +4323,15 @@
         <v/>
       </c>
       <c r="I12" s="5">
-        <f>F12-G12</f>
+        <f>C12*344</f>
         <v/>
       </c>
       <c r="J12" s="5">
         <f>H12-I12</f>
         <v/>
       </c>
-      <c r="K12" s="5">
-        <f>H12-I12</f>
-        <v/>
+      <c r="K12" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L12" s="5">
         <f>J12-K12</f>
@@ -4184,16 +4371,15 @@
         <v/>
       </c>
       <c r="I13" s="5">
-        <f>F13-G13</f>
+        <f>C13*344</f>
         <v/>
       </c>
       <c r="J13" s="5">
         <f>H13-I13</f>
         <v/>
       </c>
-      <c r="K13" s="5">
-        <f>H13-I13</f>
-        <v/>
+      <c r="K13" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L13" s="5">
         <f>J13-K13</f>
@@ -4233,16 +4419,15 @@
         <v/>
       </c>
       <c r="I14" s="5">
-        <f>F14-G14</f>
+        <f>C14*344</f>
         <v/>
       </c>
       <c r="J14" s="5">
         <f>H14-I14</f>
         <v/>
       </c>
-      <c r="K14" s="5">
-        <f>H14-I14</f>
-        <v/>
+      <c r="K14" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L14" s="5">
         <f>J14-K14</f>
@@ -4282,16 +4467,15 @@
         <v/>
       </c>
       <c r="I15" s="5">
-        <f>F15-G15</f>
+        <f>C15*344</f>
         <v/>
       </c>
       <c r="J15" s="5">
         <f>H15-I15</f>
         <v/>
       </c>
-      <c r="K15" s="5">
-        <f>H15-I15</f>
-        <v/>
+      <c r="K15" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L15" s="5">
         <f>J15-K15</f>
@@ -4331,16 +4515,15 @@
         <v/>
       </c>
       <c r="I16" s="5">
-        <f>F16-G16</f>
+        <f>C16*344</f>
         <v/>
       </c>
       <c r="J16" s="5">
         <f>H16-I16</f>
         <v/>
       </c>
-      <c r="K16" s="5">
-        <f>H16-I16</f>
-        <v/>
+      <c r="K16" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L16" s="5">
         <f>J16-K16</f>
@@ -4380,16 +4563,15 @@
         <v/>
       </c>
       <c r="I17" s="5">
-        <f>F17-G17</f>
+        <f>C17*344</f>
         <v/>
       </c>
       <c r="J17" s="5">
         <f>H17-I17</f>
         <v/>
       </c>
-      <c r="K17" s="5">
-        <f>H17-I17</f>
-        <v/>
+      <c r="K17" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L17" s="5">
         <f>J17-K17</f>
@@ -4429,16 +4611,15 @@
         <v/>
       </c>
       <c r="I18" s="5">
-        <f>F18-G18</f>
+        <f>C18*344</f>
         <v/>
       </c>
       <c r="J18" s="5">
         <f>H18-I18</f>
         <v/>
       </c>
-      <c r="K18" s="5">
-        <f>H18-I18</f>
-        <v/>
+      <c r="K18" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L18" s="5">
         <f>J18-K18</f>
@@ -4478,16 +4659,15 @@
         <v/>
       </c>
       <c r="I19" s="5">
-        <f>F19-G19</f>
+        <f>C19*344</f>
         <v/>
       </c>
       <c r="J19" s="5">
         <f>H19-I19</f>
         <v/>
       </c>
-      <c r="K19" s="5">
-        <f>H19-I19</f>
-        <v/>
+      <c r="K19" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L19" s="5">
         <f>J19-K19</f>
@@ -4527,16 +4707,15 @@
         <v/>
       </c>
       <c r="I20" s="5">
-        <f>F20-G20</f>
+        <f>C20*344</f>
         <v/>
       </c>
       <c r="J20" s="5">
         <f>H20-I20</f>
         <v/>
       </c>
-      <c r="K20" s="5">
-        <f>H20-I20</f>
-        <v/>
+      <c r="K20" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L20" s="5">
         <f>J20-K20</f>
@@ -4576,16 +4755,15 @@
         <v/>
       </c>
       <c r="I21" s="5">
-        <f>F21-G21</f>
+        <f>C21*344</f>
         <v/>
       </c>
       <c r="J21" s="5">
         <f>H21-I21</f>
         <v/>
       </c>
-      <c r="K21" s="5">
-        <f>H21-I21</f>
-        <v/>
+      <c r="K21" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L21" s="5">
         <f>J21-K21</f>
@@ -4625,16 +4803,15 @@
         <v/>
       </c>
       <c r="I22" s="5">
-        <f>F22-G22</f>
+        <f>C22*344</f>
         <v/>
       </c>
       <c r="J22" s="5">
         <f>H22-I22</f>
         <v/>
       </c>
-      <c r="K22" s="5">
-        <f>H22-I22</f>
-        <v/>
+      <c r="K22" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L22" s="5">
         <f>J22-K22</f>
@@ -4674,16 +4851,15 @@
         <v/>
       </c>
       <c r="I23" s="5">
-        <f>F23-G23</f>
+        <f>C23*344</f>
         <v/>
       </c>
       <c r="J23" s="5">
         <f>H23-I23</f>
         <v/>
       </c>
-      <c r="K23" s="5">
-        <f>H23-I23</f>
-        <v/>
+      <c r="K23" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L23" s="5">
         <f>J23-K23</f>
@@ -4723,16 +4899,15 @@
         <v/>
       </c>
       <c r="I24" s="5">
-        <f>F24-G24</f>
+        <f>C24*344</f>
         <v/>
       </c>
       <c r="J24" s="5">
         <f>H24-I24</f>
         <v/>
       </c>
-      <c r="K24" s="5">
-        <f>H24-I24</f>
-        <v/>
+      <c r="K24" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L24" s="5">
         <f>J24-K24</f>
@@ -4772,16 +4947,15 @@
         <v/>
       </c>
       <c r="I25" s="5">
-        <f>F25-G25</f>
+        <f>C25*344</f>
         <v/>
       </c>
       <c r="J25" s="5">
         <f>H25-I25</f>
         <v/>
       </c>
-      <c r="K25" s="5">
-        <f>H25-I25</f>
-        <v/>
+      <c r="K25" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L25" s="5">
         <f>J25-K25</f>
@@ -4821,16 +4995,15 @@
         <v/>
       </c>
       <c r="I26" s="5">
-        <f>F26-G26</f>
+        <f>C26*344</f>
         <v/>
       </c>
       <c r="J26" s="5">
         <f>H26-I26</f>
         <v/>
       </c>
-      <c r="K26" s="5">
-        <f>H26-I26</f>
-        <v/>
+      <c r="K26" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L26" s="5">
         <f>J26-K26</f>
@@ -4870,16 +5043,15 @@
         <v/>
       </c>
       <c r="I27" s="5">
-        <f>F27-G27</f>
+        <f>C27*344</f>
         <v/>
       </c>
       <c r="J27" s="5">
         <f>H27-I27</f>
         <v/>
       </c>
-      <c r="K27" s="5">
-        <f>H27-I27</f>
-        <v/>
+      <c r="K27" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L27" s="5">
         <f>J27-K27</f>
@@ -4919,16 +5091,15 @@
         <v/>
       </c>
       <c r="I28" s="5">
-        <f>F28-G28</f>
+        <f>C28*344</f>
         <v/>
       </c>
       <c r="J28" s="5">
         <f>H28-I28</f>
         <v/>
       </c>
-      <c r="K28" s="5">
-        <f>H28-I28</f>
-        <v/>
+      <c r="K28" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L28" s="5">
         <f>J28-K28</f>
@@ -4968,16 +5139,15 @@
         <v/>
       </c>
       <c r="I29" s="5">
-        <f>F29-G29</f>
+        <f>C29*344</f>
         <v/>
       </c>
       <c r="J29" s="5">
         <f>H29-I29</f>
         <v/>
       </c>
-      <c r="K29" s="5">
-        <f>H29-I29</f>
-        <v/>
+      <c r="K29" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L29" s="5">
         <f>J29-K29</f>
@@ -5017,16 +5187,15 @@
         <v/>
       </c>
       <c r="I30" s="5">
-        <f>F30-G30</f>
+        <f>C30*344</f>
         <v/>
       </c>
       <c r="J30" s="5">
         <f>H30-I30</f>
         <v/>
       </c>
-      <c r="K30" s="5">
-        <f>H30-I30</f>
-        <v/>
+      <c r="K30" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L30" s="5">
         <f>J30-K30</f>
@@ -5066,16 +5235,15 @@
         <v/>
       </c>
       <c r="I31" s="5">
-        <f>F31-G31</f>
+        <f>C31*344</f>
         <v/>
       </c>
       <c r="J31" s="5">
         <f>H31-I31</f>
         <v/>
       </c>
-      <c r="K31" s="5">
-        <f>H31-I31</f>
-        <v/>
+      <c r="K31" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L31" s="5">
         <f>J31-K31</f>
@@ -5115,16 +5283,15 @@
         <v/>
       </c>
       <c r="I32" s="5">
-        <f>F32-G32</f>
+        <f>C32*344</f>
         <v/>
       </c>
       <c r="J32" s="5">
         <f>H32-I32</f>
         <v/>
       </c>
-      <c r="K32" s="5">
-        <f>H32-I32</f>
-        <v/>
+      <c r="K32" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L32" s="5">
         <f>J32-K32</f>
@@ -5164,16 +5331,15 @@
         <v/>
       </c>
       <c r="I33" s="5">
-        <f>F33-G33</f>
+        <f>C33*344</f>
         <v/>
       </c>
       <c r="J33" s="5">
         <f>H33-I33</f>
         <v/>
       </c>
-      <c r="K33" s="5">
-        <f>H33-I33</f>
-        <v/>
+      <c r="K33" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L33" s="5">
         <f>J33-K33</f>
@@ -5213,16 +5379,15 @@
         <v/>
       </c>
       <c r="I34" s="5">
-        <f>F34-G34</f>
+        <f>C34*344</f>
         <v/>
       </c>
       <c r="J34" s="5">
         <f>H34-I34</f>
         <v/>
       </c>
-      <c r="K34" s="5">
-        <f>H34-I34</f>
-        <v/>
+      <c r="K34" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L34" s="5">
         <f>J34-K34</f>
@@ -5262,16 +5427,15 @@
         <v/>
       </c>
       <c r="I35" s="5">
-        <f>F35-G35</f>
+        <f>C35*344</f>
         <v/>
       </c>
       <c r="J35" s="5">
         <f>H35-I35</f>
         <v/>
       </c>
-      <c r="K35" s="5">
-        <f>H35-I35</f>
-        <v/>
+      <c r="K35" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L35" s="5">
         <f>J35-K35</f>
@@ -5311,16 +5475,15 @@
         <v/>
       </c>
       <c r="I36" s="5">
-        <f>F36-G36</f>
+        <f>C36*344</f>
         <v/>
       </c>
       <c r="J36" s="5">
         <f>H36-I36</f>
         <v/>
       </c>
-      <c r="K36" s="5">
-        <f>H36-I36</f>
-        <v/>
+      <c r="K36" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L36" s="5">
         <f>J36-K36</f>
@@ -5360,16 +5523,15 @@
         <v/>
       </c>
       <c r="I37" s="5">
-        <f>F37-G37</f>
+        <f>C37*344</f>
         <v/>
       </c>
       <c r="J37" s="5">
         <f>H37-I37</f>
         <v/>
       </c>
-      <c r="K37" s="5">
-        <f>H37-I37</f>
-        <v/>
+      <c r="K37" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L37" s="5">
         <f>J37-K37</f>
@@ -5409,16 +5571,15 @@
         <v/>
       </c>
       <c r="I38" s="5">
-        <f>F38-G38</f>
+        <f>C38*344</f>
         <v/>
       </c>
       <c r="J38" s="5">
         <f>H38-I38</f>
         <v/>
       </c>
-      <c r="K38" s="5">
-        <f>H38-I38</f>
-        <v/>
+      <c r="K38" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L38" s="5">
         <f>J38-K38</f>
@@ -5458,16 +5619,15 @@
         <v/>
       </c>
       <c r="I39" s="5">
-        <f>F39-G39</f>
+        <f>C39*344</f>
         <v/>
       </c>
       <c r="J39" s="5">
         <f>H39-I39</f>
         <v/>
       </c>
-      <c r="K39" s="5">
-        <f>H39-I39</f>
-        <v/>
+      <c r="K39" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L39" s="5">
         <f>J39-K39</f>
@@ -5507,16 +5667,15 @@
         <v/>
       </c>
       <c r="I40" s="5">
-        <f>F40-G40</f>
+        <f>C40*344</f>
         <v/>
       </c>
       <c r="J40" s="5">
         <f>H40-I40</f>
         <v/>
       </c>
-      <c r="K40" s="5">
-        <f>H40-I40</f>
-        <v/>
+      <c r="K40" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L40" s="5">
         <f>J40-K40</f>
@@ -5556,16 +5715,15 @@
         <v/>
       </c>
       <c r="I41" s="5">
-        <f>F41-G41</f>
+        <f>C41*344</f>
         <v/>
       </c>
       <c r="J41" s="5">
         <f>H41-I41</f>
         <v/>
       </c>
-      <c r="K41" s="5">
-        <f>H41-I41</f>
-        <v/>
+      <c r="K41" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L41" s="5">
         <f>J41-K41</f>
@@ -5605,16 +5763,15 @@
         <v/>
       </c>
       <c r="I42" s="5">
-        <f>F42-G42</f>
+        <f>C42*344</f>
         <v/>
       </c>
       <c r="J42" s="5">
         <f>H42-I42</f>
         <v/>
       </c>
-      <c r="K42" s="5">
-        <f>H42-I42</f>
-        <v/>
+      <c r="K42" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L42" s="5">
         <f>J42-K42</f>
@@ -5654,16 +5811,15 @@
         <v/>
       </c>
       <c r="I43" s="5">
-        <f>F43-G43</f>
+        <f>C43*344</f>
         <v/>
       </c>
       <c r="J43" s="5">
         <f>H43-I43</f>
         <v/>
       </c>
-      <c r="K43" s="5">
-        <f>H43-I43</f>
-        <v/>
+      <c r="K43" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L43" s="5">
         <f>J43-K43</f>
@@ -5703,16 +5859,15 @@
         <v/>
       </c>
       <c r="I44" s="5">
-        <f>F44-G44</f>
+        <f>C44*344</f>
         <v/>
       </c>
       <c r="J44" s="5">
         <f>H44-I44</f>
         <v/>
       </c>
-      <c r="K44" s="5">
-        <f>H44-I44</f>
-        <v/>
+      <c r="K44" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L44" s="5">
         <f>J44-K44</f>
@@ -5752,16 +5907,15 @@
         <v/>
       </c>
       <c r="I45" s="5">
-        <f>F45-G45</f>
+        <f>C45*344</f>
         <v/>
       </c>
       <c r="J45" s="5">
         <f>H45-I45</f>
         <v/>
       </c>
-      <c r="K45" s="5">
-        <f>H45-I45</f>
-        <v/>
+      <c r="K45" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L45" s="5">
         <f>J45-K45</f>
@@ -5801,16 +5955,15 @@
         <v/>
       </c>
       <c r="I46" s="5">
-        <f>F46-G46</f>
+        <f>C46*344</f>
         <v/>
       </c>
       <c r="J46" s="5">
         <f>H46-I46</f>
         <v/>
       </c>
-      <c r="K46" s="5">
-        <f>H46-I46</f>
-        <v/>
+      <c r="K46" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L46" s="5">
         <f>J46-K46</f>
@@ -5850,16 +6003,15 @@
         <v/>
       </c>
       <c r="I47" s="5">
-        <f>F47-G47</f>
+        <f>C47*344</f>
         <v/>
       </c>
       <c r="J47" s="5">
         <f>H47-I47</f>
         <v/>
       </c>
-      <c r="K47" s="5">
-        <f>H47-I47</f>
-        <v/>
+      <c r="K47" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L47" s="5">
         <f>J47-K47</f>
@@ -5899,16 +6051,15 @@
         <v/>
       </c>
       <c r="I48" s="5">
-        <f>F48-G48</f>
+        <f>C48*344</f>
         <v/>
       </c>
       <c r="J48" s="5">
         <f>H48-I48</f>
         <v/>
       </c>
-      <c r="K48" s="5">
-        <f>H48-I48</f>
-        <v/>
+      <c r="K48" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L48" s="5">
         <f>J48-K48</f>
@@ -5948,16 +6099,15 @@
         <v/>
       </c>
       <c r="I49" s="5">
-        <f>F49-G49</f>
+        <f>C49*344</f>
         <v/>
       </c>
       <c r="J49" s="5">
         <f>H49-I49</f>
         <v/>
       </c>
-      <c r="K49" s="5">
-        <f>H49-I49</f>
-        <v/>
+      <c r="K49" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L49" s="5">
         <f>J49-K49</f>
@@ -5997,16 +6147,15 @@
         <v/>
       </c>
       <c r="I50" s="5">
-        <f>F50-G50</f>
+        <f>C50*344</f>
         <v/>
       </c>
       <c r="J50" s="5">
         <f>H50-I50</f>
         <v/>
       </c>
-      <c r="K50" s="5">
-        <f>H50-I50</f>
-        <v/>
+      <c r="K50" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L50" s="5">
         <f>J50-K50</f>
@@ -6046,16 +6195,15 @@
         <v/>
       </c>
       <c r="I51" s="5">
-        <f>F51-G51</f>
+        <f>C51*344</f>
         <v/>
       </c>
       <c r="J51" s="5">
         <f>H51-I51</f>
         <v/>
       </c>
-      <c r="K51" s="5">
-        <f>H51-I51</f>
-        <v/>
+      <c r="K51" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L51" s="5">
         <f>J51-K51</f>
@@ -6095,16 +6243,15 @@
         <v/>
       </c>
       <c r="I52" s="5">
-        <f>F52-G52</f>
+        <f>C52*344</f>
         <v/>
       </c>
       <c r="J52" s="5">
         <f>H52-I52</f>
         <v/>
       </c>
-      <c r="K52" s="5">
-        <f>H52-I52</f>
-        <v/>
+      <c r="K52" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L52" s="5">
         <f>J52-K52</f>
@@ -6144,16 +6291,15 @@
         <v/>
       </c>
       <c r="I53" s="5">
-        <f>F53-G53</f>
+        <f>C53*344</f>
         <v/>
       </c>
       <c r="J53" s="5">
         <f>H53-I53</f>
         <v/>
       </c>
-      <c r="K53" s="5">
-        <f>H53-I53</f>
-        <v/>
+      <c r="K53" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L53" s="5">
         <f>J53-K53</f>
@@ -6193,16 +6339,15 @@
         <v/>
       </c>
       <c r="I54" s="5">
-        <f>F54-G54</f>
+        <f>C54*344</f>
         <v/>
       </c>
       <c r="J54" s="5">
         <f>H54-I54</f>
         <v/>
       </c>
-      <c r="K54" s="5">
-        <f>H54-I54</f>
-        <v/>
+      <c r="K54" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L54" s="5">
         <f>J54-K54</f>
@@ -6242,16 +6387,15 @@
         <v/>
       </c>
       <c r="I55" s="5">
-        <f>F55-G55</f>
+        <f>C55*344</f>
         <v/>
       </c>
       <c r="J55" s="5">
         <f>H55-I55</f>
         <v/>
       </c>
-      <c r="K55" s="5">
-        <f>H55-I55</f>
-        <v/>
+      <c r="K55" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L55" s="5">
         <f>J55-K55</f>
@@ -6291,16 +6435,15 @@
         <v/>
       </c>
       <c r="I56" s="5">
-        <f>F56-G56</f>
+        <f>C56*344</f>
         <v/>
       </c>
       <c r="J56" s="5">
         <f>H56-I56</f>
         <v/>
       </c>
-      <c r="K56" s="5">
-        <f>H56-I56</f>
-        <v/>
+      <c r="K56" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L56" s="5">
         <f>J56-K56</f>
@@ -6340,16 +6483,15 @@
         <v/>
       </c>
       <c r="I57" s="5">
-        <f>F57-G57</f>
+        <f>C57*344</f>
         <v/>
       </c>
       <c r="J57" s="5">
         <f>H57-I57</f>
         <v/>
       </c>
-      <c r="K57" s="5">
-        <f>H57-I57</f>
-        <v/>
+      <c r="K57" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L57" s="5">
         <f>J57-K57</f>
@@ -6389,16 +6531,15 @@
         <v/>
       </c>
       <c r="I58" s="5">
-        <f>F58-G58</f>
+        <f>C58*344</f>
         <v/>
       </c>
       <c r="J58" s="5">
         <f>H58-I58</f>
         <v/>
       </c>
-      <c r="K58" s="5">
-        <f>H58-I58</f>
-        <v/>
+      <c r="K58" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L58" s="5">
         <f>J58-K58</f>
@@ -6438,16 +6579,15 @@
         <v/>
       </c>
       <c r="I59" s="5">
-        <f>F59-G59</f>
+        <f>C59*344</f>
         <v/>
       </c>
       <c r="J59" s="5">
         <f>H59-I59</f>
         <v/>
       </c>
-      <c r="K59" s="5">
-        <f>H59-I59</f>
-        <v/>
+      <c r="K59" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L59" s="5">
         <f>J59-K59</f>
@@ -6487,16 +6627,15 @@
         <v/>
       </c>
       <c r="I60" s="5">
-        <f>F60-G60</f>
+        <f>C60*344</f>
         <v/>
       </c>
       <c r="J60" s="5">
         <f>H60-I60</f>
         <v/>
       </c>
-      <c r="K60" s="5">
-        <f>H60-I60</f>
-        <v/>
+      <c r="K60" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L60" s="5">
         <f>J60-K60</f>
@@ -6536,16 +6675,15 @@
         <v/>
       </c>
       <c r="I61" s="5">
-        <f>F61-G61</f>
+        <f>C61*344</f>
         <v/>
       </c>
       <c r="J61" s="5">
         <f>H61-I61</f>
         <v/>
       </c>
-      <c r="K61" s="5">
-        <f>H61-I61</f>
-        <v/>
+      <c r="K61" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L61" s="5">
         <f>J61-K61</f>
@@ -6585,16 +6723,15 @@
         <v/>
       </c>
       <c r="I62" s="5">
-        <f>F62-G62</f>
+        <f>C62*344</f>
         <v/>
       </c>
       <c r="J62" s="5">
         <f>H62-I62</f>
         <v/>
       </c>
-      <c r="K62" s="5">
-        <f>H62-I62</f>
-        <v/>
+      <c r="K62" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L62" s="5">
         <f>J62-K62</f>
@@ -6634,16 +6771,15 @@
         <v/>
       </c>
       <c r="I63" s="5">
-        <f>F63-G63</f>
+        <f>C63*344</f>
         <v/>
       </c>
       <c r="J63" s="5">
         <f>H63-I63</f>
         <v/>
       </c>
-      <c r="K63" s="5">
-        <f>H63-I63</f>
-        <v/>
+      <c r="K63" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L63" s="5">
         <f>J63-K63</f>
@@ -6683,16 +6819,15 @@
         <v/>
       </c>
       <c r="I64" s="5">
-        <f>F64-G64</f>
+        <f>C64*344</f>
         <v/>
       </c>
       <c r="J64" s="5">
         <f>H64-I64</f>
         <v/>
       </c>
-      <c r="K64" s="5">
-        <f>H64-I64</f>
-        <v/>
+      <c r="K64" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L64" s="5">
         <f>J64-K64</f>
@@ -6732,16 +6867,15 @@
         <v/>
       </c>
       <c r="I65" s="5">
-        <f>F65-G65</f>
+        <f>C65*344</f>
         <v/>
       </c>
       <c r="J65" s="5">
         <f>H65-I65</f>
         <v/>
       </c>
-      <c r="K65" s="5">
-        <f>H65-I65</f>
-        <v/>
+      <c r="K65" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L65" s="5">
         <f>J65-K65</f>
@@ -6781,16 +6915,15 @@
         <v/>
       </c>
       <c r="I66" s="5">
-        <f>F66-G66</f>
+        <f>C66*344</f>
         <v/>
       </c>
       <c r="J66" s="5">
         <f>H66-I66</f>
         <v/>
       </c>
-      <c r="K66" s="5">
-        <f>H66-I66</f>
-        <v/>
+      <c r="K66" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L66" s="5">
         <f>J66-K66</f>
@@ -6830,16 +6963,15 @@
         <v/>
       </c>
       <c r="I67" s="5">
-        <f>F67-G67</f>
+        <f>C67*344</f>
         <v/>
       </c>
       <c r="J67" s="5">
         <f>H67-I67</f>
         <v/>
       </c>
-      <c r="K67" s="5">
-        <f>H67-I67</f>
-        <v/>
+      <c r="K67" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L67" s="5">
         <f>J67-K67</f>
@@ -6879,16 +7011,15 @@
         <v/>
       </c>
       <c r="I68" s="5">
-        <f>F68-G68</f>
+        <f>C68*344</f>
         <v/>
       </c>
       <c r="J68" s="5">
         <f>H68-I68</f>
         <v/>
       </c>
-      <c r="K68" s="5">
-        <f>H68-I68</f>
-        <v/>
+      <c r="K68" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L68" s="5">
         <f>J68-K68</f>
@@ -6928,16 +7059,15 @@
         <v/>
       </c>
       <c r="I69" s="5">
-        <f>F69-G69</f>
+        <f>C69*344</f>
         <v/>
       </c>
       <c r="J69" s="5">
         <f>H69-I69</f>
         <v/>
       </c>
-      <c r="K69" s="5">
-        <f>H69-I69</f>
-        <v/>
+      <c r="K69" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L69" s="5">
         <f>J69-K69</f>
@@ -6977,16 +7107,15 @@
         <v/>
       </c>
       <c r="I70" s="5">
-        <f>F70-G70</f>
+        <f>C70*344</f>
         <v/>
       </c>
       <c r="J70" s="5">
         <f>H70-I70</f>
         <v/>
       </c>
-      <c r="K70" s="5">
-        <f>H70-I70</f>
-        <v/>
+      <c r="K70" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L70" s="5">
         <f>J70-K70</f>
@@ -7026,16 +7155,15 @@
         <v/>
       </c>
       <c r="I71" s="5">
-        <f>F71-G71</f>
+        <f>C71*344</f>
         <v/>
       </c>
       <c r="J71" s="5">
         <f>H71-I71</f>
         <v/>
       </c>
-      <c r="K71" s="5">
-        <f>H71-I71</f>
-        <v/>
+      <c r="K71" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L71" s="5">
         <f>J71-K71</f>
@@ -7075,16 +7203,15 @@
         <v/>
       </c>
       <c r="I72" s="5">
-        <f>F72-G72</f>
+        <f>C72*344</f>
         <v/>
       </c>
       <c r="J72" s="5">
         <f>H72-I72</f>
         <v/>
       </c>
-      <c r="K72" s="5">
-        <f>H72-I72</f>
-        <v/>
+      <c r="K72" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L72" s="5">
         <f>J72-K72</f>
@@ -7124,16 +7251,15 @@
         <v/>
       </c>
       <c r="I73" s="5">
-        <f>F73-G73</f>
+        <f>C73*344</f>
         <v/>
       </c>
       <c r="J73" s="5">
         <f>H73-I73</f>
         <v/>
       </c>
-      <c r="K73" s="5">
-        <f>H73-I73</f>
-        <v/>
+      <c r="K73" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L73" s="5">
         <f>J73-K73</f>
@@ -7173,16 +7299,15 @@
         <v/>
       </c>
       <c r="I74" s="5">
-        <f>F74-G74</f>
+        <f>C74*344</f>
         <v/>
       </c>
       <c r="J74" s="5">
         <f>H74-I74</f>
         <v/>
       </c>
-      <c r="K74" s="5">
-        <f>H74-I74</f>
-        <v/>
+      <c r="K74" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L74" s="5">
         <f>J74-K74</f>
@@ -7222,16 +7347,15 @@
         <v/>
       </c>
       <c r="I75" s="5">
-        <f>F75-G75</f>
+        <f>C75*344</f>
         <v/>
       </c>
       <c r="J75" s="5">
         <f>H75-I75</f>
         <v/>
       </c>
-      <c r="K75" s="5">
-        <f>H75-I75</f>
-        <v/>
+      <c r="K75" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L75" s="5">
         <f>J75-K75</f>
@@ -7271,16 +7395,15 @@
         <v/>
       </c>
       <c r="I76" s="5">
-        <f>F76-G76</f>
+        <f>C76*344</f>
         <v/>
       </c>
       <c r="J76" s="5">
         <f>H76-I76</f>
         <v/>
       </c>
-      <c r="K76" s="5">
-        <f>H76-I76</f>
-        <v/>
+      <c r="K76" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L76" s="5">
         <f>J76-K76</f>
@@ -7320,16 +7443,15 @@
         <v/>
       </c>
       <c r="I77" s="5">
-        <f>F77-G77</f>
+        <f>C77*344</f>
         <v/>
       </c>
       <c r="J77" s="5">
         <f>H77-I77</f>
         <v/>
       </c>
-      <c r="K77" s="5">
-        <f>H77-I77</f>
-        <v/>
+      <c r="K77" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L77" s="5">
         <f>J77-K77</f>
@@ -7369,16 +7491,15 @@
         <v/>
       </c>
       <c r="I78" s="5">
-        <f>F78-G78</f>
+        <f>C78*344</f>
         <v/>
       </c>
       <c r="J78" s="5">
         <f>H78-I78</f>
         <v/>
       </c>
-      <c r="K78" s="5">
-        <f>H78-I78</f>
-        <v/>
+      <c r="K78" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L78" s="5">
         <f>J78-K78</f>
@@ -7418,16 +7539,15 @@
         <v/>
       </c>
       <c r="I79" s="5">
-        <f>F79-G79</f>
+        <f>C79*344</f>
         <v/>
       </c>
       <c r="J79" s="5">
         <f>H79-I79</f>
         <v/>
       </c>
-      <c r="K79" s="5">
-        <f>H79-I79</f>
-        <v/>
+      <c r="K79" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L79" s="5">
         <f>J79-K79</f>
@@ -7467,16 +7587,15 @@
         <v/>
       </c>
       <c r="I80" s="5">
-        <f>F80-G80</f>
+        <f>C80*344</f>
         <v/>
       </c>
       <c r="J80" s="5">
         <f>H80-I80</f>
         <v/>
       </c>
-      <c r="K80" s="5">
-        <f>H80-I80</f>
-        <v/>
+      <c r="K80" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L80" s="5">
         <f>J80-K80</f>
@@ -7516,16 +7635,15 @@
         <v/>
       </c>
       <c r="I81" s="5">
-        <f>F81-G81</f>
+        <f>C81*344</f>
         <v/>
       </c>
       <c r="J81" s="5">
         <f>H81-I81</f>
         <v/>
       </c>
-      <c r="K81" s="5">
-        <f>H81-I81</f>
-        <v/>
+      <c r="K81" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L81" s="5">
         <f>J81-K81</f>
@@ -7565,16 +7683,15 @@
         <v/>
       </c>
       <c r="I82" s="5">
-        <f>F82-G82</f>
+        <f>C82*344</f>
         <v/>
       </c>
       <c r="J82" s="5">
         <f>H82-I82</f>
         <v/>
       </c>
-      <c r="K82" s="5">
-        <f>H82-I82</f>
-        <v/>
+      <c r="K82" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L82" s="5">
         <f>J82-K82</f>
@@ -7614,16 +7731,15 @@
         <v/>
       </c>
       <c r="I83" s="5">
-        <f>F83-G83</f>
+        <f>C83*344</f>
         <v/>
       </c>
       <c r="J83" s="5">
         <f>H83-I83</f>
         <v/>
       </c>
-      <c r="K83" s="5">
-        <f>H83-I83</f>
-        <v/>
+      <c r="K83" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L83" s="5">
         <f>J83-K83</f>
@@ -7663,16 +7779,15 @@
         <v/>
       </c>
       <c r="I84" s="5">
-        <f>F84-G84</f>
+        <f>C84*344</f>
         <v/>
       </c>
       <c r="J84" s="5">
         <f>H84-I84</f>
         <v/>
       </c>
-      <c r="K84" s="5">
-        <f>H84-I84</f>
-        <v/>
+      <c r="K84" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L84" s="5">
         <f>J84-K84</f>
@@ -7712,16 +7827,15 @@
         <v/>
       </c>
       <c r="I85" s="5">
-        <f>F85-G85</f>
+        <f>C85*344</f>
         <v/>
       </c>
       <c r="J85" s="5">
         <f>H85-I85</f>
         <v/>
       </c>
-      <c r="K85" s="5">
-        <f>H85-I85</f>
-        <v/>
+      <c r="K85" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L85" s="5">
         <f>J85-K85</f>
@@ -7761,16 +7875,15 @@
         <v/>
       </c>
       <c r="I86" s="5">
-        <f>F86-G86</f>
+        <f>C86*344</f>
         <v/>
       </c>
       <c r="J86" s="5">
         <f>H86-I86</f>
         <v/>
       </c>
-      <c r="K86" s="5">
-        <f>H86-I86</f>
-        <v/>
+      <c r="K86" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L86" s="5">
         <f>J86-K86</f>
@@ -7810,16 +7923,15 @@
         <v/>
       </c>
       <c r="I87" s="5">
-        <f>F87-G87</f>
+        <f>C87*344</f>
         <v/>
       </c>
       <c r="J87" s="5">
         <f>H87-I87</f>
         <v/>
       </c>
-      <c r="K87" s="5">
-        <f>H87-I87</f>
-        <v/>
+      <c r="K87" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L87" s="5">
         <f>J87-K87</f>
@@ -7859,16 +7971,15 @@
         <v/>
       </c>
       <c r="I88" s="5">
-        <f>F88-G88</f>
+        <f>C88*344</f>
         <v/>
       </c>
       <c r="J88" s="5">
         <f>H88-I88</f>
         <v/>
       </c>
-      <c r="K88" s="5">
-        <f>H88-I88</f>
-        <v/>
+      <c r="K88" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L88" s="5">
         <f>J88-K88</f>
@@ -7908,16 +8019,15 @@
         <v/>
       </c>
       <c r="I89" s="5">
-        <f>F89-G89</f>
+        <f>C89*344</f>
         <v/>
       </c>
       <c r="J89" s="5">
         <f>H89-I89</f>
         <v/>
       </c>
-      <c r="K89" s="5">
-        <f>H89-I89</f>
-        <v/>
+      <c r="K89" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L89" s="5">
         <f>J89-K89</f>
@@ -7957,16 +8067,15 @@
         <v/>
       </c>
       <c r="I90" s="5">
-        <f>F90-G90</f>
+        <f>C90*344</f>
         <v/>
       </c>
       <c r="J90" s="5">
         <f>H90-I90</f>
         <v/>
       </c>
-      <c r="K90" s="5">
-        <f>H90-I90</f>
-        <v/>
+      <c r="K90" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L90" s="5">
         <f>J90-K90</f>
@@ -8006,16 +8115,15 @@
         <v/>
       </c>
       <c r="I91" s="5">
-        <f>F91-G91</f>
+        <f>C91*344</f>
         <v/>
       </c>
       <c r="J91" s="5">
         <f>H91-I91</f>
         <v/>
       </c>
-      <c r="K91" s="5">
-        <f>H91-I91</f>
-        <v/>
+      <c r="K91" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L91" s="5">
         <f>J91-K91</f>
@@ -8055,16 +8163,15 @@
         <v/>
       </c>
       <c r="I92" s="5">
-        <f>F92-G92</f>
+        <f>C92*344</f>
         <v/>
       </c>
       <c r="J92" s="5">
         <f>H92-I92</f>
         <v/>
       </c>
-      <c r="K92" s="5">
-        <f>H92-I92</f>
-        <v/>
+      <c r="K92" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L92" s="5">
         <f>J92-K92</f>
@@ -8104,16 +8211,15 @@
         <v/>
       </c>
       <c r="I93" s="5">
-        <f>F93-G93</f>
+        <f>C93*344</f>
         <v/>
       </c>
       <c r="J93" s="5">
         <f>H93-I93</f>
         <v/>
       </c>
-      <c r="K93" s="5">
-        <f>H93-I93</f>
-        <v/>
+      <c r="K93" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L93" s="5">
         <f>J93-K93</f>
@@ -8153,16 +8259,15 @@
         <v/>
       </c>
       <c r="I94" s="5">
-        <f>F94-G94</f>
+        <f>C94*344</f>
         <v/>
       </c>
       <c r="J94" s="5">
         <f>H94-I94</f>
         <v/>
       </c>
-      <c r="K94" s="5">
-        <f>H94-I94</f>
-        <v/>
+      <c r="K94" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L94" s="5">
         <f>J94-K94</f>
@@ -8202,16 +8307,15 @@
         <v/>
       </c>
       <c r="I95" s="5">
-        <f>F95-G95</f>
+        <f>C95*344</f>
         <v/>
       </c>
       <c r="J95" s="5">
         <f>H95-I95</f>
         <v/>
       </c>
-      <c r="K95" s="5">
-        <f>H95-I95</f>
-        <v/>
+      <c r="K95" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L95" s="5">
         <f>J95-K95</f>
@@ -8251,16 +8355,15 @@
         <v/>
       </c>
       <c r="I96" s="5">
-        <f>F96-G96</f>
+        <f>C96*344</f>
         <v/>
       </c>
       <c r="J96" s="5">
         <f>H96-I96</f>
         <v/>
       </c>
-      <c r="K96" s="5">
-        <f>H96-I96</f>
-        <v/>
+      <c r="K96" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L96" s="5">
         <f>J96-K96</f>
@@ -8300,16 +8403,15 @@
         <v/>
       </c>
       <c r="I97" s="5">
-        <f>F97-G97</f>
+        <f>C97*344</f>
         <v/>
       </c>
       <c r="J97" s="5">
         <f>H97-I97</f>
         <v/>
       </c>
-      <c r="K97" s="5">
-        <f>H97-I97</f>
-        <v/>
+      <c r="K97" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L97" s="5">
         <f>J97-K97</f>
@@ -8349,16 +8451,15 @@
         <v/>
       </c>
       <c r="I98" s="5">
-        <f>F98-G98</f>
+        <f>C98*344</f>
         <v/>
       </c>
       <c r="J98" s="5">
         <f>H98-I98</f>
         <v/>
       </c>
-      <c r="K98" s="5">
-        <f>H98-I98</f>
-        <v/>
+      <c r="K98" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L98" s="5">
         <f>J98-K98</f>
@@ -8398,16 +8499,15 @@
         <v/>
       </c>
       <c r="I99" s="5">
-        <f>F99-G99</f>
+        <f>C99*344</f>
         <v/>
       </c>
       <c r="J99" s="5">
         <f>H99-I99</f>
         <v/>
       </c>
-      <c r="K99" s="5">
-        <f>H99-I99</f>
-        <v/>
+      <c r="K99" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L99" s="5">
         <f>J99-K99</f>
@@ -8447,16 +8547,15 @@
         <v/>
       </c>
       <c r="I100" s="5">
-        <f>F100-G100</f>
+        <f>C100*344</f>
         <v/>
       </c>
       <c r="J100" s="5">
         <f>H100-I100</f>
         <v/>
       </c>
-      <c r="K100" s="5">
-        <f>H100-I100</f>
-        <v/>
+      <c r="K100" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L100" s="5">
         <f>J100-K100</f>
@@ -8496,16 +8595,15 @@
         <v/>
       </c>
       <c r="I101" s="5">
-        <f>F101-G101</f>
+        <f>C101*344</f>
         <v/>
       </c>
       <c r="J101" s="5">
         <f>H101-I101</f>
         <v/>
       </c>
-      <c r="K101" s="5">
-        <f>H101-I101</f>
-        <v/>
+      <c r="K101" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L101" s="5">
         <f>J101-K101</f>
@@ -8545,16 +8643,15 @@
         <v/>
       </c>
       <c r="I102" s="5">
-        <f>F102-G102</f>
+        <f>C102*344</f>
         <v/>
       </c>
       <c r="J102" s="5">
         <f>H102-I102</f>
         <v/>
       </c>
-      <c r="K102" s="5">
-        <f>H102-I102</f>
-        <v/>
+      <c r="K102" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L102" s="5">
         <f>J102-K102</f>
@@ -8594,16 +8691,15 @@
         <v/>
       </c>
       <c r="I103" s="5">
-        <f>F103-G103</f>
+        <f>C103*344</f>
         <v/>
       </c>
       <c r="J103" s="5">
         <f>H103-I103</f>
         <v/>
       </c>
-      <c r="K103" s="5">
-        <f>H103-I103</f>
-        <v/>
+      <c r="K103" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L103" s="5">
         <f>J103-K103</f>
@@ -8643,16 +8739,15 @@
         <v/>
       </c>
       <c r="I104" s="5">
-        <f>F104-G104</f>
+        <f>C104*344</f>
         <v/>
       </c>
       <c r="J104" s="5">
         <f>H104-I104</f>
         <v/>
       </c>
-      <c r="K104" s="5">
-        <f>H104-I104</f>
-        <v/>
+      <c r="K104" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L104" s="5">
         <f>J104-K104</f>
@@ -8692,16 +8787,15 @@
         <v/>
       </c>
       <c r="I105" s="5">
-        <f>F105-G105</f>
+        <f>C105*344</f>
         <v/>
       </c>
       <c r="J105" s="5">
         <f>H105-I105</f>
         <v/>
       </c>
-      <c r="K105" s="5">
-        <f>H105-I105</f>
-        <v/>
+      <c r="K105" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L105" s="5">
         <f>J105-K105</f>
@@ -8741,16 +8835,15 @@
         <v/>
       </c>
       <c r="I106" s="5">
-        <f>F106-G106</f>
+        <f>C106*344</f>
         <v/>
       </c>
       <c r="J106" s="5">
         <f>H106-I106</f>
         <v/>
       </c>
-      <c r="K106" s="5">
-        <f>H106-I106</f>
-        <v/>
+      <c r="K106" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L106" s="5">
         <f>J106-K106</f>
@@ -8790,16 +8883,15 @@
         <v/>
       </c>
       <c r="I107" s="5">
-        <f>F107-G107</f>
+        <f>C107*344</f>
         <v/>
       </c>
       <c r="J107" s="5">
         <f>H107-I107</f>
         <v/>
       </c>
-      <c r="K107" s="5">
-        <f>H107-I107</f>
-        <v/>
+      <c r="K107" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L107" s="5">
         <f>J107-K107</f>
@@ -8839,16 +8931,15 @@
         <v/>
       </c>
       <c r="I108" s="5">
-        <f>F108-G108</f>
+        <f>C108*344</f>
         <v/>
       </c>
       <c r="J108" s="5">
         <f>H108-I108</f>
         <v/>
       </c>
-      <c r="K108" s="5">
-        <f>H108-I108</f>
-        <v/>
+      <c r="K108" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L108" s="5">
         <f>J108-K108</f>
@@ -8888,16 +8979,15 @@
         <v/>
       </c>
       <c r="I109" s="5">
-        <f>F109-G109</f>
+        <f>C109*344</f>
         <v/>
       </c>
       <c r="J109" s="5">
         <f>H109-I109</f>
         <v/>
       </c>
-      <c r="K109" s="5">
-        <f>H109-I109</f>
-        <v/>
+      <c r="K109" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L109" s="5">
         <f>J109-K109</f>
@@ -8937,16 +9027,15 @@
         <v/>
       </c>
       <c r="I110" s="5">
-        <f>F110-G110</f>
+        <f>C110*344</f>
         <v/>
       </c>
       <c r="J110" s="5">
         <f>H110-I110</f>
         <v/>
       </c>
-      <c r="K110" s="5">
-        <f>H110-I110</f>
-        <v/>
+      <c r="K110" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L110" s="5">
         <f>J110-K110</f>
@@ -8986,16 +9075,15 @@
         <v/>
       </c>
       <c r="I111" s="5">
-        <f>F111-G111</f>
+        <f>C111*344</f>
         <v/>
       </c>
       <c r="J111" s="5">
         <f>H111-I111</f>
         <v/>
       </c>
-      <c r="K111" s="5">
-        <f>H111-I111</f>
-        <v/>
+      <c r="K111" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L111" s="5">
         <f>J111-K111</f>
@@ -9035,16 +9123,15 @@
         <v/>
       </c>
       <c r="I112" s="5">
-        <f>F112-G112</f>
+        <f>C112*344</f>
         <v/>
       </c>
       <c r="J112" s="5">
         <f>H112-I112</f>
         <v/>
       </c>
-      <c r="K112" s="5">
-        <f>H112-I112</f>
-        <v/>
+      <c r="K112" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L112" s="5">
         <f>J112-K112</f>
@@ -9084,16 +9171,15 @@
         <v/>
       </c>
       <c r="I113" s="5">
-        <f>F113-G113</f>
+        <f>C113*344</f>
         <v/>
       </c>
       <c r="J113" s="5">
         <f>H113-I113</f>
         <v/>
       </c>
-      <c r="K113" s="5">
-        <f>H113-I113</f>
-        <v/>
+      <c r="K113" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L113" s="5">
         <f>J113-K113</f>
@@ -9133,16 +9219,15 @@
         <v/>
       </c>
       <c r="I114" s="5">
-        <f>F114-G114</f>
+        <f>C114*344</f>
         <v/>
       </c>
       <c r="J114" s="5">
         <f>H114-I114</f>
         <v/>
       </c>
-      <c r="K114" s="5">
-        <f>H114-I114</f>
-        <v/>
+      <c r="K114" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L114" s="5">
         <f>J114-K114</f>
@@ -9182,16 +9267,15 @@
         <v/>
       </c>
       <c r="I115" s="5">
-        <f>F115-G115</f>
+        <f>C115*344</f>
         <v/>
       </c>
       <c r="J115" s="5">
         <f>H115-I115</f>
         <v/>
       </c>
-      <c r="K115" s="5">
-        <f>H115-I115</f>
-        <v/>
+      <c r="K115" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L115" s="5">
         <f>J115-K115</f>
@@ -9231,16 +9315,15 @@
         <v/>
       </c>
       <c r="I116" s="5">
-        <f>F116-G116</f>
+        <f>C116*344</f>
         <v/>
       </c>
       <c r="J116" s="5">
         <f>H116-I116</f>
         <v/>
       </c>
-      <c r="K116" s="5">
-        <f>H116-I116</f>
-        <v/>
+      <c r="K116" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L116" s="5">
         <f>J116-K116</f>
@@ -9280,16 +9363,15 @@
         <v/>
       </c>
       <c r="I117" s="5">
-        <f>F117-G117</f>
+        <f>C117*344</f>
         <v/>
       </c>
       <c r="J117" s="5">
         <f>H117-I117</f>
         <v/>
       </c>
-      <c r="K117" s="5">
-        <f>H117-I117</f>
-        <v/>
+      <c r="K117" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L117" s="5">
         <f>J117-K117</f>
@@ -9329,16 +9411,15 @@
         <v/>
       </c>
       <c r="I118" s="5">
-        <f>F118-G118</f>
+        <f>C118*344</f>
         <v/>
       </c>
       <c r="J118" s="5">
         <f>H118-I118</f>
         <v/>
       </c>
-      <c r="K118" s="5">
-        <f>H118-I118</f>
-        <v/>
+      <c r="K118" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L118" s="5">
         <f>J118-K118</f>
@@ -9378,16 +9459,15 @@
         <v/>
       </c>
       <c r="I119" s="5">
-        <f>F119-G119</f>
+        <f>C119*344</f>
         <v/>
       </c>
       <c r="J119" s="5">
         <f>H119-I119</f>
         <v/>
       </c>
-      <c r="K119" s="5">
-        <f>H119-I119</f>
-        <v/>
+      <c r="K119" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L119" s="5">
         <f>J119-K119</f>
@@ -9427,16 +9507,15 @@
         <v/>
       </c>
       <c r="I120" s="5">
-        <f>F120-G120</f>
+        <f>C120*344</f>
         <v/>
       </c>
       <c r="J120" s="5">
         <f>H120-I120</f>
         <v/>
       </c>
-      <c r="K120" s="5">
-        <f>H120-I120</f>
-        <v/>
+      <c r="K120" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L120" s="5">
         <f>J120-K120</f>
@@ -9476,16 +9555,15 @@
         <v/>
       </c>
       <c r="I121" s="5">
-        <f>F121-G121</f>
+        <f>C121*344</f>
         <v/>
       </c>
       <c r="J121" s="5">
         <f>H121-I121</f>
         <v/>
       </c>
-      <c r="K121" s="5">
-        <f>H121-I121</f>
-        <v/>
+      <c r="K121" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L121" s="5">
         <f>J121-K121</f>
@@ -9525,16 +9603,15 @@
         <v/>
       </c>
       <c r="I122" s="5">
-        <f>F122-G122</f>
+        <f>C122*344</f>
         <v/>
       </c>
       <c r="J122" s="5">
         <f>H122-I122</f>
         <v/>
       </c>
-      <c r="K122" s="5">
-        <f>H122-I122</f>
-        <v/>
+      <c r="K122" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L122" s="5">
         <f>J122-K122</f>
@@ -9574,16 +9651,15 @@
         <v/>
       </c>
       <c r="I123" s="5">
-        <f>F123-G123</f>
+        <f>C123*344</f>
         <v/>
       </c>
       <c r="J123" s="5">
         <f>H123-I123</f>
         <v/>
       </c>
-      <c r="K123" s="5">
-        <f>H123-I123</f>
-        <v/>
+      <c r="K123" s="7" t="n">
+        <v>6281.43</v>
       </c>
       <c r="L123" s="5">
         <f>J123-K123</f>
@@ -9666,7 +9742,7 @@
         <v/>
       </c>
       <c r="C4" s="5">
-        <f>SUM('10-Year Monthly Projections'!G4:G15)</f>
+        <f>SUM('10-Year Monthly Projections'!I4:I15)</f>
         <v/>
       </c>
       <c r="D4" s="5">
@@ -9674,7 +9750,7 @@
         <v/>
       </c>
       <c r="E4" s="5">
-        <f>SUM('10-Year Monthly Projections'!I4:I15)</f>
+        <f>SUM('10-Year Monthly Projections'!K4:K15)</f>
         <v/>
       </c>
       <c r="F4" s="5">
@@ -9699,7 +9775,7 @@
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>SUM('10-Year Monthly Projections'!G16:G27)</f>
+        <f>SUM('10-Year Monthly Projections'!I16:I27)</f>
         <v/>
       </c>
       <c r="D5" s="5">
@@ -9707,7 +9783,7 @@
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>SUM('10-Year Monthly Projections'!I16:I27)</f>
+        <f>SUM('10-Year Monthly Projections'!K16:K27)</f>
         <v/>
       </c>
       <c r="F5" s="5">
@@ -9732,7 +9808,7 @@
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>SUM('10-Year Monthly Projections'!G28:G39)</f>
+        <f>SUM('10-Year Monthly Projections'!I28:I39)</f>
         <v/>
       </c>
       <c r="D6" s="5">
@@ -9740,7 +9816,7 @@
         <v/>
       </c>
       <c r="E6" s="5">
-        <f>SUM('10-Year Monthly Projections'!I28:I39)</f>
+        <f>SUM('10-Year Monthly Projections'!K28:K39)</f>
         <v/>
       </c>
       <c r="F6" s="5">
@@ -9765,7 +9841,7 @@
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>SUM('10-Year Monthly Projections'!G40:G51)</f>
+        <f>SUM('10-Year Monthly Projections'!I40:I51)</f>
         <v/>
       </c>
       <c r="D7" s="5">
@@ -9773,7 +9849,7 @@
         <v/>
       </c>
       <c r="E7" s="5">
-        <f>SUM('10-Year Monthly Projections'!I40:I51)</f>
+        <f>SUM('10-Year Monthly Projections'!K40:K51)</f>
         <v/>
       </c>
       <c r="F7" s="5">
@@ -9798,7 +9874,7 @@
         <v/>
       </c>
       <c r="C8" s="5">
-        <f>SUM('10-Year Monthly Projections'!G52:G63)</f>
+        <f>SUM('10-Year Monthly Projections'!I52:I63)</f>
         <v/>
       </c>
       <c r="D8" s="5">
@@ -9806,7 +9882,7 @@
         <v/>
       </c>
       <c r="E8" s="5">
-        <f>SUM('10-Year Monthly Projections'!I52:I63)</f>
+        <f>SUM('10-Year Monthly Projections'!K52:K63)</f>
         <v/>
       </c>
       <c r="F8" s="5">
@@ -9831,7 +9907,7 @@
         <v/>
       </c>
       <c r="C9" s="5">
-        <f>SUM('10-Year Monthly Projections'!G64:G75)</f>
+        <f>SUM('10-Year Monthly Projections'!I64:I75)</f>
         <v/>
       </c>
       <c r="D9" s="5">
@@ -9839,7 +9915,7 @@
         <v/>
       </c>
       <c r="E9" s="5">
-        <f>SUM('10-Year Monthly Projections'!I64:I75)</f>
+        <f>SUM('10-Year Monthly Projections'!K64:K75)</f>
         <v/>
       </c>
       <c r="F9" s="5">
@@ -9864,7 +9940,7 @@
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>SUM('10-Year Monthly Projections'!G76:G87)</f>
+        <f>SUM('10-Year Monthly Projections'!I76:I87)</f>
         <v/>
       </c>
       <c r="D10" s="5">
@@ -9872,7 +9948,7 @@
         <v/>
       </c>
       <c r="E10" s="5">
-        <f>SUM('10-Year Monthly Projections'!I76:I87)</f>
+        <f>SUM('10-Year Monthly Projections'!K76:K87)</f>
         <v/>
       </c>
       <c r="F10" s="5">
@@ -9897,7 +9973,7 @@
         <v/>
       </c>
       <c r="C11" s="5">
-        <f>SUM('10-Year Monthly Projections'!G88:G99)</f>
+        <f>SUM('10-Year Monthly Projections'!I88:I99)</f>
         <v/>
       </c>
       <c r="D11" s="5">
@@ -9905,7 +9981,7 @@
         <v/>
       </c>
       <c r="E11" s="5">
-        <f>SUM('10-Year Monthly Projections'!I88:I99)</f>
+        <f>SUM('10-Year Monthly Projections'!K88:K99)</f>
         <v/>
       </c>
       <c r="F11" s="5">
@@ -9930,7 +10006,7 @@
         <v/>
       </c>
       <c r="C12" s="5">
-        <f>SUM('10-Year Monthly Projections'!G100:G111)</f>
+        <f>SUM('10-Year Monthly Projections'!I100:I111)</f>
         <v/>
       </c>
       <c r="D12" s="5">
@@ -9938,7 +10014,7 @@
         <v/>
       </c>
       <c r="E12" s="5">
-        <f>SUM('10-Year Monthly Projections'!I100:I111)</f>
+        <f>SUM('10-Year Monthly Projections'!K100:K111)</f>
         <v/>
       </c>
       <c r="F12" s="5">
@@ -9963,7 +10039,7 @@
         <v/>
       </c>
       <c r="C13" s="5">
-        <f>SUM('10-Year Monthly Projections'!G112:G123)</f>
+        <f>SUM('10-Year Monthly Projections'!I112:I123)</f>
         <v/>
       </c>
       <c r="D13" s="5">
@@ -9971,7 +10047,7 @@
         <v/>
       </c>
       <c r="E13" s="5">
-        <f>SUM('10-Year Monthly Projections'!I112:I123)</f>
+        <f>SUM('10-Year Monthly Projections'!K112:K123)</f>
         <v/>
       </c>
       <c r="F13" s="5">
@@ -10049,40 +10125,41 @@
           <t>Existing Debt Payoff</t>
         </is>
       </c>
-      <c r="B8" s="5">
-        <f>'Renovation Budget Detail'!E156</f>
-        <v/>
+      <c r="B8" s="5" t="n">
+        <v>150000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Room Renovation (40 rooms @ $15k)</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>600000</v>
+          <t>Renovation &amp; Amenities</t>
+        </is>
+      </c>
+      <c r="B9" s="5">
+        <f>'Renovation Budget Detail'!E156</f>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Room Renovation (43 rooms)</t>
+          <t>Contingency (10%)</t>
         </is>
       </c>
       <c r="B10" s="5">
-        <f>'Renovation Budget Detail'!E$13</f>
+        <f>'Renovation Budget Detail'!E157</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Jobsite Costs &amp; Contingency</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>25000</v>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL USES</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>SUM(B8:B10)</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -10094,6 +10171,13 @@
       <c r="B12" s="3">
         <f>SUM(B8:B11)</f>
         <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Note: 40% renovation grant potential ($240k) available but not assumed in projections</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -12747,7 +12831,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">

--- a/Hotel-Brendle-Loan-Application.xlsx
+++ b/Hotel-Brendle-Loan-Application.xlsx
@@ -12909,8 +12909,8 @@
       <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10">
-        <f>'10-Year Monthly Projections'!E4</f>
+      <c r="C10" s="14">
+        <f>'10-Year Monthly Projections'!C4*'10-Year Monthly Projections'!D4</f>
         <v/>
       </c>
       <c r="D10" s="14">
@@ -12937,8 +12937,8 @@
       <c r="B11" t="n">
         <v>2</v>
       </c>
-      <c r="C11">
-        <f>'10-Year Monthly Projections'!E5</f>
+      <c r="C11" s="14">
+        <f>'10-Year Monthly Projections'!C5*'10-Year Monthly Projections'!D5</f>
         <v/>
       </c>
       <c r="D11" s="14">
@@ -12965,8 +12965,8 @@
       <c r="B12" t="n">
         <v>3</v>
       </c>
-      <c r="C12">
-        <f>'10-Year Monthly Projections'!E6</f>
+      <c r="C12" s="14">
+        <f>'10-Year Monthly Projections'!C6*'10-Year Monthly Projections'!D6</f>
         <v/>
       </c>
       <c r="D12" s="14">
@@ -12993,8 +12993,8 @@
       <c r="B13" t="n">
         <v>4</v>
       </c>
-      <c r="C13">
-        <f>'10-Year Monthly Projections'!E7</f>
+      <c r="C13" s="14">
+        <f>'10-Year Monthly Projections'!C7*'10-Year Monthly Projections'!D7</f>
         <v/>
       </c>
       <c r="D13" s="14">
@@ -13021,8 +13021,8 @@
       <c r="B14" t="n">
         <v>5</v>
       </c>
-      <c r="C14">
-        <f>'10-Year Monthly Projections'!E8</f>
+      <c r="C14" s="14">
+        <f>'10-Year Monthly Projections'!C8*'10-Year Monthly Projections'!D8</f>
         <v/>
       </c>
       <c r="D14" s="14">
@@ -13049,8 +13049,8 @@
       <c r="B15" t="n">
         <v>6</v>
       </c>
-      <c r="C15">
-        <f>'10-Year Monthly Projections'!E9</f>
+      <c r="C15" s="14">
+        <f>'10-Year Monthly Projections'!C9*'10-Year Monthly Projections'!D9</f>
         <v/>
       </c>
       <c r="D15" s="14">
@@ -13077,8 +13077,8 @@
       <c r="B16" t="n">
         <v>7</v>
       </c>
-      <c r="C16">
-        <f>'10-Year Monthly Projections'!E10</f>
+      <c r="C16" s="14">
+        <f>'10-Year Monthly Projections'!C10*'10-Year Monthly Projections'!D10</f>
         <v/>
       </c>
       <c r="D16" s="14">
@@ -13105,8 +13105,8 @@
       <c r="B17" t="n">
         <v>8</v>
       </c>
-      <c r="C17">
-        <f>'10-Year Monthly Projections'!E11</f>
+      <c r="C17" s="14">
+        <f>'10-Year Monthly Projections'!C11*'10-Year Monthly Projections'!D11</f>
         <v/>
       </c>
       <c r="D17" s="14">
@@ -13133,8 +13133,8 @@
       <c r="B18" t="n">
         <v>9</v>
       </c>
-      <c r="C18">
-        <f>'10-Year Monthly Projections'!E12</f>
+      <c r="C18" s="14">
+        <f>'10-Year Monthly Projections'!C12*'10-Year Monthly Projections'!D12</f>
         <v/>
       </c>
       <c r="D18" s="14">
@@ -13161,8 +13161,8 @@
       <c r="B19" t="n">
         <v>10</v>
       </c>
-      <c r="C19">
-        <f>'10-Year Monthly Projections'!E13</f>
+      <c r="C19" s="14">
+        <f>'10-Year Monthly Projections'!C13*'10-Year Monthly Projections'!D13</f>
         <v/>
       </c>
       <c r="D19" s="14">
@@ -13189,8 +13189,8 @@
       <c r="B20" t="n">
         <v>11</v>
       </c>
-      <c r="C20">
-        <f>'10-Year Monthly Projections'!E14</f>
+      <c r="C20" s="14">
+        <f>'10-Year Monthly Projections'!C14*'10-Year Monthly Projections'!D14</f>
         <v/>
       </c>
       <c r="D20" s="14">
@@ -13217,8 +13217,8 @@
       <c r="B21" t="n">
         <v>12</v>
       </c>
-      <c r="C21">
-        <f>'10-Year Monthly Projections'!E15</f>
+      <c r="C21" s="14">
+        <f>'10-Year Monthly Projections'!C15*'10-Year Monthly Projections'!D15</f>
         <v/>
       </c>
       <c r="D21" s="14">
@@ -13245,8 +13245,8 @@
       <c r="B22" t="n">
         <v>1</v>
       </c>
-      <c r="C22">
-        <f>'10-Year Monthly Projections'!E16</f>
+      <c r="C22" s="14">
+        <f>'10-Year Monthly Projections'!C16*'10-Year Monthly Projections'!D16</f>
         <v/>
       </c>
       <c r="D22" s="14">
@@ -13273,8 +13273,8 @@
       <c r="B23" t="n">
         <v>2</v>
       </c>
-      <c r="C23">
-        <f>'10-Year Monthly Projections'!E17</f>
+      <c r="C23" s="14">
+        <f>'10-Year Monthly Projections'!C17*'10-Year Monthly Projections'!D17</f>
         <v/>
       </c>
       <c r="D23" s="14">
@@ -13301,8 +13301,8 @@
       <c r="B24" t="n">
         <v>3</v>
       </c>
-      <c r="C24">
-        <f>'10-Year Monthly Projections'!E18</f>
+      <c r="C24" s="14">
+        <f>'10-Year Monthly Projections'!C18*'10-Year Monthly Projections'!D18</f>
         <v/>
       </c>
       <c r="D24" s="14">
@@ -13329,8 +13329,8 @@
       <c r="B25" t="n">
         <v>4</v>
       </c>
-      <c r="C25">
-        <f>'10-Year Monthly Projections'!E19</f>
+      <c r="C25" s="14">
+        <f>'10-Year Monthly Projections'!C19*'10-Year Monthly Projections'!D19</f>
         <v/>
       </c>
       <c r="D25" s="14">
@@ -13357,8 +13357,8 @@
       <c r="B26" t="n">
         <v>5</v>
       </c>
-      <c r="C26">
-        <f>'10-Year Monthly Projections'!E20</f>
+      <c r="C26" s="14">
+        <f>'10-Year Monthly Projections'!C20*'10-Year Monthly Projections'!D20</f>
         <v/>
       </c>
       <c r="D26" s="14">
@@ -13385,8 +13385,8 @@
       <c r="B27" t="n">
         <v>6</v>
       </c>
-      <c r="C27">
-        <f>'10-Year Monthly Projections'!E21</f>
+      <c r="C27" s="14">
+        <f>'10-Year Monthly Projections'!C21*'10-Year Monthly Projections'!D21</f>
         <v/>
       </c>
       <c r="D27" s="14">
@@ -13413,8 +13413,8 @@
       <c r="B28" t="n">
         <v>7</v>
       </c>
-      <c r="C28">
-        <f>'10-Year Monthly Projections'!E22</f>
+      <c r="C28" s="14">
+        <f>'10-Year Monthly Projections'!C22*'10-Year Monthly Projections'!D22</f>
         <v/>
       </c>
       <c r="D28" s="14">
@@ -13441,8 +13441,8 @@
       <c r="B29" t="n">
         <v>8</v>
       </c>
-      <c r="C29">
-        <f>'10-Year Monthly Projections'!E23</f>
+      <c r="C29" s="14">
+        <f>'10-Year Monthly Projections'!C23*'10-Year Monthly Projections'!D23</f>
         <v/>
       </c>
       <c r="D29" s="14">
@@ -13469,8 +13469,8 @@
       <c r="B30" t="n">
         <v>9</v>
       </c>
-      <c r="C30">
-        <f>'10-Year Monthly Projections'!E24</f>
+      <c r="C30" s="14">
+        <f>'10-Year Monthly Projections'!C24*'10-Year Monthly Projections'!D24</f>
         <v/>
       </c>
       <c r="D30" s="14">
@@ -13497,8 +13497,8 @@
       <c r="B31" t="n">
         <v>10</v>
       </c>
-      <c r="C31">
-        <f>'10-Year Monthly Projections'!E25</f>
+      <c r="C31" s="14">
+        <f>'10-Year Monthly Projections'!C25*'10-Year Monthly Projections'!D25</f>
         <v/>
       </c>
       <c r="D31" s="14">
@@ -13525,8 +13525,8 @@
       <c r="B32" t="n">
         <v>11</v>
       </c>
-      <c r="C32">
-        <f>'10-Year Monthly Projections'!E26</f>
+      <c r="C32" s="14">
+        <f>'10-Year Monthly Projections'!C26*'10-Year Monthly Projections'!D26</f>
         <v/>
       </c>
       <c r="D32" s="14">
@@ -13553,8 +13553,8 @@
       <c r="B33" t="n">
         <v>12</v>
       </c>
-      <c r="C33">
-        <f>'10-Year Monthly Projections'!E27</f>
+      <c r="C33" s="14">
+        <f>'10-Year Monthly Projections'!C27*'10-Year Monthly Projections'!D27</f>
         <v/>
       </c>
       <c r="D33" s="14">
@@ -13581,8 +13581,8 @@
       <c r="B34" t="n">
         <v>1</v>
       </c>
-      <c r="C34">
-        <f>'10-Year Monthly Projections'!E28</f>
+      <c r="C34" s="14">
+        <f>'10-Year Monthly Projections'!C28*'10-Year Monthly Projections'!D28</f>
         <v/>
       </c>
       <c r="D34" s="14">
@@ -13609,8 +13609,8 @@
       <c r="B35" t="n">
         <v>2</v>
       </c>
-      <c r="C35">
-        <f>'10-Year Monthly Projections'!E29</f>
+      <c r="C35" s="14">
+        <f>'10-Year Monthly Projections'!C29*'10-Year Monthly Projections'!D29</f>
         <v/>
       </c>
       <c r="D35" s="14">
@@ -13637,8 +13637,8 @@
       <c r="B36" t="n">
         <v>3</v>
       </c>
-      <c r="C36">
-        <f>'10-Year Monthly Projections'!E30</f>
+      <c r="C36" s="14">
+        <f>'10-Year Monthly Projections'!C30*'10-Year Monthly Projections'!D30</f>
         <v/>
       </c>
       <c r="D36" s="14">
@@ -13665,8 +13665,8 @@
       <c r="B37" t="n">
         <v>4</v>
       </c>
-      <c r="C37">
-        <f>'10-Year Monthly Projections'!E31</f>
+      <c r="C37" s="14">
+        <f>'10-Year Monthly Projections'!C31*'10-Year Monthly Projections'!D31</f>
         <v/>
       </c>
       <c r="D37" s="14">
@@ -13693,8 +13693,8 @@
       <c r="B38" t="n">
         <v>5</v>
       </c>
-      <c r="C38">
-        <f>'10-Year Monthly Projections'!E32</f>
+      <c r="C38" s="14">
+        <f>'10-Year Monthly Projections'!C32*'10-Year Monthly Projections'!D32</f>
         <v/>
       </c>
       <c r="D38" s="14">
@@ -13721,8 +13721,8 @@
       <c r="B39" t="n">
         <v>6</v>
       </c>
-      <c r="C39">
-        <f>'10-Year Monthly Projections'!E33</f>
+      <c r="C39" s="14">
+        <f>'10-Year Monthly Projections'!C33*'10-Year Monthly Projections'!D33</f>
         <v/>
       </c>
       <c r="D39" s="14">
@@ -13749,8 +13749,8 @@
       <c r="B40" t="n">
         <v>7</v>
       </c>
-      <c r="C40">
-        <f>'10-Year Monthly Projections'!E34</f>
+      <c r="C40" s="14">
+        <f>'10-Year Monthly Projections'!C34*'10-Year Monthly Projections'!D34</f>
         <v/>
       </c>
       <c r="D40" s="14">
@@ -13777,8 +13777,8 @@
       <c r="B41" t="n">
         <v>8</v>
       </c>
-      <c r="C41">
-        <f>'10-Year Monthly Projections'!E35</f>
+      <c r="C41" s="14">
+        <f>'10-Year Monthly Projections'!C35*'10-Year Monthly Projections'!D35</f>
         <v/>
       </c>
       <c r="D41" s="14">
@@ -13805,8 +13805,8 @@
       <c r="B42" t="n">
         <v>9</v>
       </c>
-      <c r="C42">
-        <f>'10-Year Monthly Projections'!E36</f>
+      <c r="C42" s="14">
+        <f>'10-Year Monthly Projections'!C36*'10-Year Monthly Projections'!D36</f>
         <v/>
       </c>
       <c r="D42" s="14">
@@ -13833,8 +13833,8 @@
       <c r="B43" t="n">
         <v>10</v>
       </c>
-      <c r="C43">
-        <f>'10-Year Monthly Projections'!E37</f>
+      <c r="C43" s="14">
+        <f>'10-Year Monthly Projections'!C37*'10-Year Monthly Projections'!D37</f>
         <v/>
       </c>
       <c r="D43" s="14">
@@ -13861,8 +13861,8 @@
       <c r="B44" t="n">
         <v>11</v>
       </c>
-      <c r="C44">
-        <f>'10-Year Monthly Projections'!E38</f>
+      <c r="C44" s="14">
+        <f>'10-Year Monthly Projections'!C38*'10-Year Monthly Projections'!D38</f>
         <v/>
       </c>
       <c r="D44" s="14">
@@ -13889,8 +13889,8 @@
       <c r="B45" t="n">
         <v>12</v>
       </c>
-      <c r="C45">
-        <f>'10-Year Monthly Projections'!E39</f>
+      <c r="C45" s="14">
+        <f>'10-Year Monthly Projections'!C39*'10-Year Monthly Projections'!D39</f>
         <v/>
       </c>
       <c r="D45" s="14">
@@ -13917,8 +13917,8 @@
       <c r="B46" t="n">
         <v>1</v>
       </c>
-      <c r="C46">
-        <f>'10-Year Monthly Projections'!E40</f>
+      <c r="C46" s="14">
+        <f>'10-Year Monthly Projections'!C40*'10-Year Monthly Projections'!D40</f>
         <v/>
       </c>
       <c r="D46" s="14">
@@ -13945,8 +13945,8 @@
       <c r="B47" t="n">
         <v>2</v>
       </c>
-      <c r="C47">
-        <f>'10-Year Monthly Projections'!E41</f>
+      <c r="C47" s="14">
+        <f>'10-Year Monthly Projections'!C41*'10-Year Monthly Projections'!D41</f>
         <v/>
       </c>
       <c r="D47" s="14">
@@ -13973,8 +13973,8 @@
       <c r="B48" t="n">
         <v>3</v>
       </c>
-      <c r="C48">
-        <f>'10-Year Monthly Projections'!E42</f>
+      <c r="C48" s="14">
+        <f>'10-Year Monthly Projections'!C42*'10-Year Monthly Projections'!D42</f>
         <v/>
       </c>
       <c r="D48" s="14">
@@ -14001,8 +14001,8 @@
       <c r="B49" t="n">
         <v>4</v>
       </c>
-      <c r="C49">
-        <f>'10-Year Monthly Projections'!E43</f>
+      <c r="C49" s="14">
+        <f>'10-Year Monthly Projections'!C43*'10-Year Monthly Projections'!D43</f>
         <v/>
       </c>
       <c r="D49" s="14">
@@ -14029,8 +14029,8 @@
       <c r="B50" t="n">
         <v>5</v>
       </c>
-      <c r="C50">
-        <f>'10-Year Monthly Projections'!E44</f>
+      <c r="C50" s="14">
+        <f>'10-Year Monthly Projections'!C44*'10-Year Monthly Projections'!D44</f>
         <v/>
       </c>
       <c r="D50" s="14">
@@ -14057,8 +14057,8 @@
       <c r="B51" t="n">
         <v>6</v>
       </c>
-      <c r="C51">
-        <f>'10-Year Monthly Projections'!E45</f>
+      <c r="C51" s="14">
+        <f>'10-Year Monthly Projections'!C45*'10-Year Monthly Projections'!D45</f>
         <v/>
       </c>
       <c r="D51" s="14">
@@ -14085,8 +14085,8 @@
       <c r="B52" t="n">
         <v>7</v>
       </c>
-      <c r="C52">
-        <f>'10-Year Monthly Projections'!E46</f>
+      <c r="C52" s="14">
+        <f>'10-Year Monthly Projections'!C46*'10-Year Monthly Projections'!D46</f>
         <v/>
       </c>
       <c r="D52" s="14">
@@ -14113,8 +14113,8 @@
       <c r="B53" t="n">
         <v>8</v>
       </c>
-      <c r="C53">
-        <f>'10-Year Monthly Projections'!E47</f>
+      <c r="C53" s="14">
+        <f>'10-Year Monthly Projections'!C47*'10-Year Monthly Projections'!D47</f>
         <v/>
       </c>
       <c r="D53" s="14">
@@ -14141,8 +14141,8 @@
       <c r="B54" t="n">
         <v>9</v>
       </c>
-      <c r="C54">
-        <f>'10-Year Monthly Projections'!E48</f>
+      <c r="C54" s="14">
+        <f>'10-Year Monthly Projections'!C48*'10-Year Monthly Projections'!D48</f>
         <v/>
       </c>
       <c r="D54" s="14">
@@ -14169,8 +14169,8 @@
       <c r="B55" t="n">
         <v>10</v>
       </c>
-      <c r="C55">
-        <f>'10-Year Monthly Projections'!E49</f>
+      <c r="C55" s="14">
+        <f>'10-Year Monthly Projections'!C49*'10-Year Monthly Projections'!D49</f>
         <v/>
       </c>
       <c r="D55" s="14">
@@ -14197,8 +14197,8 @@
       <c r="B56" t="n">
         <v>11</v>
       </c>
-      <c r="C56">
-        <f>'10-Year Monthly Projections'!E50</f>
+      <c r="C56" s="14">
+        <f>'10-Year Monthly Projections'!C50*'10-Year Monthly Projections'!D50</f>
         <v/>
       </c>
       <c r="D56" s="14">
@@ -14225,8 +14225,8 @@
       <c r="B57" t="n">
         <v>12</v>
       </c>
-      <c r="C57">
-        <f>'10-Year Monthly Projections'!E51</f>
+      <c r="C57" s="14">
+        <f>'10-Year Monthly Projections'!C51*'10-Year Monthly Projections'!D51</f>
         <v/>
       </c>
       <c r="D57" s="14">
@@ -14253,8 +14253,8 @@
       <c r="B58" t="n">
         <v>1</v>
       </c>
-      <c r="C58">
-        <f>'10-Year Monthly Projections'!E52</f>
+      <c r="C58" s="14">
+        <f>'10-Year Monthly Projections'!C52*'10-Year Monthly Projections'!D52</f>
         <v/>
       </c>
       <c r="D58" s="14">
@@ -14281,8 +14281,8 @@
       <c r="B59" t="n">
         <v>2</v>
       </c>
-      <c r="C59">
-        <f>'10-Year Monthly Projections'!E53</f>
+      <c r="C59" s="14">
+        <f>'10-Year Monthly Projections'!C53*'10-Year Monthly Projections'!D53</f>
         <v/>
       </c>
       <c r="D59" s="14">
@@ -14309,8 +14309,8 @@
       <c r="B60" t="n">
         <v>3</v>
       </c>
-      <c r="C60">
-        <f>'10-Year Monthly Projections'!E54</f>
+      <c r="C60" s="14">
+        <f>'10-Year Monthly Projections'!C54*'10-Year Monthly Projections'!D54</f>
         <v/>
       </c>
       <c r="D60" s="14">
@@ -14337,8 +14337,8 @@
       <c r="B61" t="n">
         <v>4</v>
       </c>
-      <c r="C61">
-        <f>'10-Year Monthly Projections'!E55</f>
+      <c r="C61" s="14">
+        <f>'10-Year Monthly Projections'!C55*'10-Year Monthly Projections'!D55</f>
         <v/>
       </c>
       <c r="D61" s="14">
@@ -14365,8 +14365,8 @@
       <c r="B62" t="n">
         <v>5</v>
       </c>
-      <c r="C62">
-        <f>'10-Year Monthly Projections'!E56</f>
+      <c r="C62" s="14">
+        <f>'10-Year Monthly Projections'!C56*'10-Year Monthly Projections'!D56</f>
         <v/>
       </c>
       <c r="D62" s="14">
@@ -14393,8 +14393,8 @@
       <c r="B63" t="n">
         <v>6</v>
       </c>
-      <c r="C63">
-        <f>'10-Year Monthly Projections'!E57</f>
+      <c r="C63" s="14">
+        <f>'10-Year Monthly Projections'!C57*'10-Year Monthly Projections'!D57</f>
         <v/>
       </c>
       <c r="D63" s="14">
@@ -14421,8 +14421,8 @@
       <c r="B64" t="n">
         <v>7</v>
       </c>
-      <c r="C64">
-        <f>'10-Year Monthly Projections'!E58</f>
+      <c r="C64" s="14">
+        <f>'10-Year Monthly Projections'!C58*'10-Year Monthly Projections'!D58</f>
         <v/>
       </c>
       <c r="D64" s="14">
@@ -14449,8 +14449,8 @@
       <c r="B65" t="n">
         <v>8</v>
       </c>
-      <c r="C65">
-        <f>'10-Year Monthly Projections'!E59</f>
+      <c r="C65" s="14">
+        <f>'10-Year Monthly Projections'!C59*'10-Year Monthly Projections'!D59</f>
         <v/>
       </c>
       <c r="D65" s="14">
@@ -14477,8 +14477,8 @@
       <c r="B66" t="n">
         <v>9</v>
       </c>
-      <c r="C66">
-        <f>'10-Year Monthly Projections'!E60</f>
+      <c r="C66" s="14">
+        <f>'10-Year Monthly Projections'!C60*'10-Year Monthly Projections'!D60</f>
         <v/>
       </c>
       <c r="D66" s="14">
@@ -14505,8 +14505,8 @@
       <c r="B67" t="n">
         <v>10</v>
       </c>
-      <c r="C67">
-        <f>'10-Year Monthly Projections'!E61</f>
+      <c r="C67" s="14">
+        <f>'10-Year Monthly Projections'!C61*'10-Year Monthly Projections'!D61</f>
         <v/>
       </c>
       <c r="D67" s="14">
@@ -14533,8 +14533,8 @@
       <c r="B68" t="n">
         <v>11</v>
       </c>
-      <c r="C68">
-        <f>'10-Year Monthly Projections'!E62</f>
+      <c r="C68" s="14">
+        <f>'10-Year Monthly Projections'!C62*'10-Year Monthly Projections'!D62</f>
         <v/>
       </c>
       <c r="D68" s="14">
@@ -14561,8 +14561,8 @@
       <c r="B69" t="n">
         <v>12</v>
       </c>
-      <c r="C69">
-        <f>'10-Year Monthly Projections'!E63</f>
+      <c r="C69" s="14">
+        <f>'10-Year Monthly Projections'!C63*'10-Year Monthly Projections'!D63</f>
         <v/>
       </c>
       <c r="D69" s="14">
@@ -14589,8 +14589,8 @@
       <c r="B70" t="n">
         <v>1</v>
       </c>
-      <c r="C70">
-        <f>'10-Year Monthly Projections'!E64</f>
+      <c r="C70" s="14">
+        <f>'10-Year Monthly Projections'!C64*'10-Year Monthly Projections'!D64</f>
         <v/>
       </c>
       <c r="D70" s="14">
@@ -14617,8 +14617,8 @@
       <c r="B71" t="n">
         <v>2</v>
       </c>
-      <c r="C71">
-        <f>'10-Year Monthly Projections'!E65</f>
+      <c r="C71" s="14">
+        <f>'10-Year Monthly Projections'!C65*'10-Year Monthly Projections'!D65</f>
         <v/>
       </c>
       <c r="D71" s="14">
@@ -14645,8 +14645,8 @@
       <c r="B72" t="n">
         <v>3</v>
       </c>
-      <c r="C72">
-        <f>'10-Year Monthly Projections'!E66</f>
+      <c r="C72" s="14">
+        <f>'10-Year Monthly Projections'!C66*'10-Year Monthly Projections'!D66</f>
         <v/>
       </c>
       <c r="D72" s="14">
@@ -14673,8 +14673,8 @@
       <c r="B73" t="n">
         <v>4</v>
       </c>
-      <c r="C73">
-        <f>'10-Year Monthly Projections'!E67</f>
+      <c r="C73" s="14">
+        <f>'10-Year Monthly Projections'!C67*'10-Year Monthly Projections'!D67</f>
         <v/>
       </c>
       <c r="D73" s="14">
@@ -14701,8 +14701,8 @@
       <c r="B74" t="n">
         <v>5</v>
       </c>
-      <c r="C74">
-        <f>'10-Year Monthly Projections'!E68</f>
+      <c r="C74" s="14">
+        <f>'10-Year Monthly Projections'!C68*'10-Year Monthly Projections'!D68</f>
         <v/>
       </c>
       <c r="D74" s="14">
@@ -14729,8 +14729,8 @@
       <c r="B75" t="n">
         <v>6</v>
       </c>
-      <c r="C75">
-        <f>'10-Year Monthly Projections'!E69</f>
+      <c r="C75" s="14">
+        <f>'10-Year Monthly Projections'!C69*'10-Year Monthly Projections'!D69</f>
         <v/>
       </c>
       <c r="D75" s="14">
@@ -14757,8 +14757,8 @@
       <c r="B76" t="n">
         <v>7</v>
       </c>
-      <c r="C76">
-        <f>'10-Year Monthly Projections'!E70</f>
+      <c r="C76" s="14">
+        <f>'10-Year Monthly Projections'!C70*'10-Year Monthly Projections'!D70</f>
         <v/>
       </c>
       <c r="D76" s="14">
@@ -14785,8 +14785,8 @@
       <c r="B77" t="n">
         <v>8</v>
       </c>
-      <c r="C77">
-        <f>'10-Year Monthly Projections'!E71</f>
+      <c r="C77" s="14">
+        <f>'10-Year Monthly Projections'!C71*'10-Year Monthly Projections'!D71</f>
         <v/>
       </c>
       <c r="D77" s="14">
@@ -14813,8 +14813,8 @@
       <c r="B78" t="n">
         <v>9</v>
       </c>
-      <c r="C78">
-        <f>'10-Year Monthly Projections'!E72</f>
+      <c r="C78" s="14">
+        <f>'10-Year Monthly Projections'!C72*'10-Year Monthly Projections'!D72</f>
         <v/>
       </c>
       <c r="D78" s="14">
@@ -14841,8 +14841,8 @@
       <c r="B79" t="n">
         <v>10</v>
       </c>
-      <c r="C79">
-        <f>'10-Year Monthly Projections'!E73</f>
+      <c r="C79" s="14">
+        <f>'10-Year Monthly Projections'!C73*'10-Year Monthly Projections'!D73</f>
         <v/>
       </c>
       <c r="D79" s="14">
@@ -14869,8 +14869,8 @@
       <c r="B80" t="n">
         <v>11</v>
       </c>
-      <c r="C80">
-        <f>'10-Year Monthly Projections'!E74</f>
+      <c r="C80" s="14">
+        <f>'10-Year Monthly Projections'!C74*'10-Year Monthly Projections'!D74</f>
         <v/>
       </c>
       <c r="D80" s="14">
@@ -14897,8 +14897,8 @@
       <c r="B81" t="n">
         <v>12</v>
       </c>
-      <c r="C81">
-        <f>'10-Year Monthly Projections'!E75</f>
+      <c r="C81" s="14">
+        <f>'10-Year Monthly Projections'!C75*'10-Year Monthly Projections'!D75</f>
         <v/>
       </c>
       <c r="D81" s="14">
@@ -14925,8 +14925,8 @@
       <c r="B82" t="n">
         <v>1</v>
       </c>
-      <c r="C82">
-        <f>'10-Year Monthly Projections'!E76</f>
+      <c r="C82" s="14">
+        <f>'10-Year Monthly Projections'!C76*'10-Year Monthly Projections'!D76</f>
         <v/>
       </c>
       <c r="D82" s="14">
@@ -14953,8 +14953,8 @@
       <c r="B83" t="n">
         <v>2</v>
       </c>
-      <c r="C83">
-        <f>'10-Year Monthly Projections'!E77</f>
+      <c r="C83" s="14">
+        <f>'10-Year Monthly Projections'!C77*'10-Year Monthly Projections'!D77</f>
         <v/>
       </c>
       <c r="D83" s="14">
@@ -14981,8 +14981,8 @@
       <c r="B84" t="n">
         <v>3</v>
       </c>
-      <c r="C84">
-        <f>'10-Year Monthly Projections'!E78</f>
+      <c r="C84" s="14">
+        <f>'10-Year Monthly Projections'!C78*'10-Year Monthly Projections'!D78</f>
         <v/>
       </c>
       <c r="D84" s="14">
@@ -15009,8 +15009,8 @@
       <c r="B85" t="n">
         <v>4</v>
       </c>
-      <c r="C85">
-        <f>'10-Year Monthly Projections'!E79</f>
+      <c r="C85" s="14">
+        <f>'10-Year Monthly Projections'!C79*'10-Year Monthly Projections'!D79</f>
         <v/>
       </c>
       <c r="D85" s="14">
@@ -15037,8 +15037,8 @@
       <c r="B86" t="n">
         <v>5</v>
       </c>
-      <c r="C86">
-        <f>'10-Year Monthly Projections'!E80</f>
+      <c r="C86" s="14">
+        <f>'10-Year Monthly Projections'!C80*'10-Year Monthly Projections'!D80</f>
         <v/>
       </c>
       <c r="D86" s="14">
@@ -15065,8 +15065,8 @@
       <c r="B87" t="n">
         <v>6</v>
       </c>
-      <c r="C87">
-        <f>'10-Year Monthly Projections'!E81</f>
+      <c r="C87" s="14">
+        <f>'10-Year Monthly Projections'!C81*'10-Year Monthly Projections'!D81</f>
         <v/>
       </c>
       <c r="D87" s="14">
@@ -15093,8 +15093,8 @@
       <c r="B88" t="n">
         <v>7</v>
       </c>
-      <c r="C88">
-        <f>'10-Year Monthly Projections'!E82</f>
+      <c r="C88" s="14">
+        <f>'10-Year Monthly Projections'!C82*'10-Year Monthly Projections'!D82</f>
         <v/>
       </c>
       <c r="D88" s="14">
@@ -15121,8 +15121,8 @@
       <c r="B89" t="n">
         <v>8</v>
       </c>
-      <c r="C89">
-        <f>'10-Year Monthly Projections'!E83</f>
+      <c r="C89" s="14">
+        <f>'10-Year Monthly Projections'!C83*'10-Year Monthly Projections'!D83</f>
         <v/>
       </c>
       <c r="D89" s="14">
@@ -15149,8 +15149,8 @@
       <c r="B90" t="n">
         <v>9</v>
       </c>
-      <c r="C90">
-        <f>'10-Year Monthly Projections'!E84</f>
+      <c r="C90" s="14">
+        <f>'10-Year Monthly Projections'!C84*'10-Year Monthly Projections'!D84</f>
         <v/>
       </c>
       <c r="D90" s="14">
@@ -15177,8 +15177,8 @@
       <c r="B91" t="n">
         <v>10</v>
       </c>
-      <c r="C91">
-        <f>'10-Year Monthly Projections'!E85</f>
+      <c r="C91" s="14">
+        <f>'10-Year Monthly Projections'!C85*'10-Year Monthly Projections'!D85</f>
         <v/>
       </c>
       <c r="D91" s="14">
@@ -15205,8 +15205,8 @@
       <c r="B92" t="n">
         <v>11</v>
       </c>
-      <c r="C92">
-        <f>'10-Year Monthly Projections'!E86</f>
+      <c r="C92" s="14">
+        <f>'10-Year Monthly Projections'!C86*'10-Year Monthly Projections'!D86</f>
         <v/>
       </c>
       <c r="D92" s="14">
@@ -15233,8 +15233,8 @@
       <c r="B93" t="n">
         <v>12</v>
       </c>
-      <c r="C93">
-        <f>'10-Year Monthly Projections'!E87</f>
+      <c r="C93" s="14">
+        <f>'10-Year Monthly Projections'!C87*'10-Year Monthly Projections'!D87</f>
         <v/>
       </c>
       <c r="D93" s="14">
@@ -15261,8 +15261,8 @@
       <c r="B94" t="n">
         <v>1</v>
       </c>
-      <c r="C94">
-        <f>'10-Year Monthly Projections'!E88</f>
+      <c r="C94" s="14">
+        <f>'10-Year Monthly Projections'!C88*'10-Year Monthly Projections'!D88</f>
         <v/>
       </c>
       <c r="D94" s="14">
@@ -15289,8 +15289,8 @@
       <c r="B95" t="n">
         <v>2</v>
       </c>
-      <c r="C95">
-        <f>'10-Year Monthly Projections'!E89</f>
+      <c r="C95" s="14">
+        <f>'10-Year Monthly Projections'!C89*'10-Year Monthly Projections'!D89</f>
         <v/>
       </c>
       <c r="D95" s="14">
@@ -15317,8 +15317,8 @@
       <c r="B96" t="n">
         <v>3</v>
       </c>
-      <c r="C96">
-        <f>'10-Year Monthly Projections'!E90</f>
+      <c r="C96" s="14">
+        <f>'10-Year Monthly Projections'!C90*'10-Year Monthly Projections'!D90</f>
         <v/>
       </c>
       <c r="D96" s="14">
@@ -15345,8 +15345,8 @@
       <c r="B97" t="n">
         <v>4</v>
       </c>
-      <c r="C97">
-        <f>'10-Year Monthly Projections'!E91</f>
+      <c r="C97" s="14">
+        <f>'10-Year Monthly Projections'!C91*'10-Year Monthly Projections'!D91</f>
         <v/>
       </c>
       <c r="D97" s="14">
@@ -15373,8 +15373,8 @@
       <c r="B98" t="n">
         <v>5</v>
       </c>
-      <c r="C98">
-        <f>'10-Year Monthly Projections'!E92</f>
+      <c r="C98" s="14">
+        <f>'10-Year Monthly Projections'!C92*'10-Year Monthly Projections'!D92</f>
         <v/>
       </c>
       <c r="D98" s="14">
@@ -15401,8 +15401,8 @@
       <c r="B99" t="n">
         <v>6</v>
       </c>
-      <c r="C99">
-        <f>'10-Year Monthly Projections'!E93</f>
+      <c r="C99" s="14">
+        <f>'10-Year Monthly Projections'!C93*'10-Year Monthly Projections'!D93</f>
         <v/>
       </c>
       <c r="D99" s="14">
@@ -15429,8 +15429,8 @@
       <c r="B100" t="n">
         <v>7</v>
       </c>
-      <c r="C100">
-        <f>'10-Year Monthly Projections'!E94</f>
+      <c r="C100" s="14">
+        <f>'10-Year Monthly Projections'!C94*'10-Year Monthly Projections'!D94</f>
         <v/>
       </c>
       <c r="D100" s="14">
@@ -15457,8 +15457,8 @@
       <c r="B101" t="n">
         <v>8</v>
       </c>
-      <c r="C101">
-        <f>'10-Year Monthly Projections'!E95</f>
+      <c r="C101" s="14">
+        <f>'10-Year Monthly Projections'!C95*'10-Year Monthly Projections'!D95</f>
         <v/>
       </c>
       <c r="D101" s="14">
@@ -15485,8 +15485,8 @@
       <c r="B102" t="n">
         <v>9</v>
       </c>
-      <c r="C102">
-        <f>'10-Year Monthly Projections'!E96</f>
+      <c r="C102" s="14">
+        <f>'10-Year Monthly Projections'!C96*'10-Year Monthly Projections'!D96</f>
         <v/>
       </c>
       <c r="D102" s="14">
@@ -15513,8 +15513,8 @@
       <c r="B103" t="n">
         <v>10</v>
       </c>
-      <c r="C103">
-        <f>'10-Year Monthly Projections'!E97</f>
+      <c r="C103" s="14">
+        <f>'10-Year Monthly Projections'!C97*'10-Year Monthly Projections'!D97</f>
         <v/>
       </c>
       <c r="D103" s="14">
@@ -15541,8 +15541,8 @@
       <c r="B104" t="n">
         <v>11</v>
       </c>
-      <c r="C104">
-        <f>'10-Year Monthly Projections'!E98</f>
+      <c r="C104" s="14">
+        <f>'10-Year Monthly Projections'!C98*'10-Year Monthly Projections'!D98</f>
         <v/>
       </c>
       <c r="D104" s="14">
@@ -15569,8 +15569,8 @@
       <c r="B105" t="n">
         <v>12</v>
       </c>
-      <c r="C105">
-        <f>'10-Year Monthly Projections'!E99</f>
+      <c r="C105" s="14">
+        <f>'10-Year Monthly Projections'!C99*'10-Year Monthly Projections'!D99</f>
         <v/>
       </c>
       <c r="D105" s="14">
@@ -15597,8 +15597,8 @@
       <c r="B106" t="n">
         <v>1</v>
       </c>
-      <c r="C106">
-        <f>'10-Year Monthly Projections'!E100</f>
+      <c r="C106" s="14">
+        <f>'10-Year Monthly Projections'!C100*'10-Year Monthly Projections'!D100</f>
         <v/>
       </c>
       <c r="D106" s="14">
@@ -15625,8 +15625,8 @@
       <c r="B107" t="n">
         <v>2</v>
       </c>
-      <c r="C107">
-        <f>'10-Year Monthly Projections'!E101</f>
+      <c r="C107" s="14">
+        <f>'10-Year Monthly Projections'!C101*'10-Year Monthly Projections'!D101</f>
         <v/>
       </c>
       <c r="D107" s="14">
@@ -15653,8 +15653,8 @@
       <c r="B108" t="n">
         <v>3</v>
       </c>
-      <c r="C108">
-        <f>'10-Year Monthly Projections'!E102</f>
+      <c r="C108" s="14">
+        <f>'10-Year Monthly Projections'!C102*'10-Year Monthly Projections'!D102</f>
         <v/>
       </c>
       <c r="D108" s="14">
@@ -15681,8 +15681,8 @@
       <c r="B109" t="n">
         <v>4</v>
       </c>
-      <c r="C109">
-        <f>'10-Year Monthly Projections'!E103</f>
+      <c r="C109" s="14">
+        <f>'10-Year Monthly Projections'!C103*'10-Year Monthly Projections'!D103</f>
         <v/>
       </c>
       <c r="D109" s="14">
@@ -15709,8 +15709,8 @@
       <c r="B110" t="n">
         <v>5</v>
       </c>
-      <c r="C110">
-        <f>'10-Year Monthly Projections'!E104</f>
+      <c r="C110" s="14">
+        <f>'10-Year Monthly Projections'!C104*'10-Year Monthly Projections'!D104</f>
         <v/>
       </c>
       <c r="D110" s="14">
@@ -15737,8 +15737,8 @@
       <c r="B111" t="n">
         <v>6</v>
       </c>
-      <c r="C111">
-        <f>'10-Year Monthly Projections'!E105</f>
+      <c r="C111" s="14">
+        <f>'10-Year Monthly Projections'!C105*'10-Year Monthly Projections'!D105</f>
         <v/>
       </c>
       <c r="D111" s="14">
@@ -15765,8 +15765,8 @@
       <c r="B112" t="n">
         <v>7</v>
       </c>
-      <c r="C112">
-        <f>'10-Year Monthly Projections'!E106</f>
+      <c r="C112" s="14">
+        <f>'10-Year Monthly Projections'!C106*'10-Year Monthly Projections'!D106</f>
         <v/>
       </c>
       <c r="D112" s="14">
@@ -15793,8 +15793,8 @@
       <c r="B113" t="n">
         <v>8</v>
       </c>
-      <c r="C113">
-        <f>'10-Year Monthly Projections'!E107</f>
+      <c r="C113" s="14">
+        <f>'10-Year Monthly Projections'!C107*'10-Year Monthly Projections'!D107</f>
         <v/>
       </c>
       <c r="D113" s="14">
@@ -15821,8 +15821,8 @@
       <c r="B114" t="n">
         <v>9</v>
       </c>
-      <c r="C114">
-        <f>'10-Year Monthly Projections'!E108</f>
+      <c r="C114" s="14">
+        <f>'10-Year Monthly Projections'!C108*'10-Year Monthly Projections'!D108</f>
         <v/>
       </c>
       <c r="D114" s="14">
@@ -15849,8 +15849,8 @@
       <c r="B115" t="n">
         <v>10</v>
       </c>
-      <c r="C115">
-        <f>'10-Year Monthly Projections'!E109</f>
+      <c r="C115" s="14">
+        <f>'10-Year Monthly Projections'!C109*'10-Year Monthly Projections'!D109</f>
         <v/>
       </c>
       <c r="D115" s="14">
@@ -15877,8 +15877,8 @@
       <c r="B116" t="n">
         <v>11</v>
       </c>
-      <c r="C116">
-        <f>'10-Year Monthly Projections'!E110</f>
+      <c r="C116" s="14">
+        <f>'10-Year Monthly Projections'!C110*'10-Year Monthly Projections'!D110</f>
         <v/>
       </c>
       <c r="D116" s="14">
@@ -15905,8 +15905,8 @@
       <c r="B117" t="n">
         <v>12</v>
       </c>
-      <c r="C117">
-        <f>'10-Year Monthly Projections'!E111</f>
+      <c r="C117" s="14">
+        <f>'10-Year Monthly Projections'!C111*'10-Year Monthly Projections'!D111</f>
         <v/>
       </c>
       <c r="D117" s="14">
@@ -15933,8 +15933,8 @@
       <c r="B118" t="n">
         <v>1</v>
       </c>
-      <c r="C118">
-        <f>'10-Year Monthly Projections'!E112</f>
+      <c r="C118" s="14">
+        <f>'10-Year Monthly Projections'!C112*'10-Year Monthly Projections'!D112</f>
         <v/>
       </c>
       <c r="D118" s="14">
@@ -15961,8 +15961,8 @@
       <c r="B119" t="n">
         <v>2</v>
       </c>
-      <c r="C119">
-        <f>'10-Year Monthly Projections'!E113</f>
+      <c r="C119" s="14">
+        <f>'10-Year Monthly Projections'!C113*'10-Year Monthly Projections'!D113</f>
         <v/>
       </c>
       <c r="D119" s="14">
@@ -15989,8 +15989,8 @@
       <c r="B120" t="n">
         <v>3</v>
       </c>
-      <c r="C120">
-        <f>'10-Year Monthly Projections'!E114</f>
+      <c r="C120" s="14">
+        <f>'10-Year Monthly Projections'!C114*'10-Year Monthly Projections'!D114</f>
         <v/>
       </c>
       <c r="D120" s="14">
@@ -16017,8 +16017,8 @@
       <c r="B121" t="n">
         <v>4</v>
       </c>
-      <c r="C121">
-        <f>'10-Year Monthly Projections'!E115</f>
+      <c r="C121" s="14">
+        <f>'10-Year Monthly Projections'!C115*'10-Year Monthly Projections'!D115</f>
         <v/>
       </c>
       <c r="D121" s="14">
@@ -16045,8 +16045,8 @@
       <c r="B122" t="n">
         <v>5</v>
       </c>
-      <c r="C122">
-        <f>'10-Year Monthly Projections'!E116</f>
+      <c r="C122" s="14">
+        <f>'10-Year Monthly Projections'!C116*'10-Year Monthly Projections'!D116</f>
         <v/>
       </c>
       <c r="D122" s="14">
@@ -16073,8 +16073,8 @@
       <c r="B123" t="n">
         <v>6</v>
       </c>
-      <c r="C123">
-        <f>'10-Year Monthly Projections'!E117</f>
+      <c r="C123" s="14">
+        <f>'10-Year Monthly Projections'!C117*'10-Year Monthly Projections'!D117</f>
         <v/>
       </c>
       <c r="D123" s="14">
@@ -16101,8 +16101,8 @@
       <c r="B124" t="n">
         <v>7</v>
       </c>
-      <c r="C124">
-        <f>'10-Year Monthly Projections'!E118</f>
+      <c r="C124" s="14">
+        <f>'10-Year Monthly Projections'!C118*'10-Year Monthly Projections'!D118</f>
         <v/>
       </c>
       <c r="D124" s="14">
@@ -16129,8 +16129,8 @@
       <c r="B125" t="n">
         <v>8</v>
       </c>
-      <c r="C125">
-        <f>'10-Year Monthly Projections'!E119</f>
+      <c r="C125" s="14">
+        <f>'10-Year Monthly Projections'!C119*'10-Year Monthly Projections'!D119</f>
         <v/>
       </c>
       <c r="D125" s="14">
@@ -16157,8 +16157,8 @@
       <c r="B126" t="n">
         <v>9</v>
       </c>
-      <c r="C126">
-        <f>'10-Year Monthly Projections'!E120</f>
+      <c r="C126" s="14">
+        <f>'10-Year Monthly Projections'!C120*'10-Year Monthly Projections'!D120</f>
         <v/>
       </c>
       <c r="D126" s="14">
@@ -16185,8 +16185,8 @@
       <c r="B127" t="n">
         <v>10</v>
       </c>
-      <c r="C127">
-        <f>'10-Year Monthly Projections'!E121</f>
+      <c r="C127" s="14">
+        <f>'10-Year Monthly Projections'!C121*'10-Year Monthly Projections'!D121</f>
         <v/>
       </c>
       <c r="D127" s="14">
@@ -16213,8 +16213,8 @@
       <c r="B128" t="n">
         <v>11</v>
       </c>
-      <c r="C128">
-        <f>'10-Year Monthly Projections'!E122</f>
+      <c r="C128" s="14">
+        <f>'10-Year Monthly Projections'!C122*'10-Year Monthly Projections'!D122</f>
         <v/>
       </c>
       <c r="D128" s="14">
@@ -16241,8 +16241,8 @@
       <c r="B129" t="n">
         <v>12</v>
       </c>
-      <c r="C129">
-        <f>'10-Year Monthly Projections'!E123</f>
+      <c r="C129" s="14">
+        <f>'10-Year Monthly Projections'!C123*'10-Year Monthly Projections'!D123</f>
         <v/>
       </c>
       <c r="D129" s="14">

--- a/Hotel-Brendle-Loan-Application.xlsx
+++ b/Hotel-Brendle-Loan-Application.xlsx
@@ -35,7 +35,7 @@
     <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -69,8 +69,72 @@
       <b val="1"/>
       <color rgb="00008000"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E3A5F"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C8102E"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C8102E"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C8102E"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00008000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C8102E"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -81,6 +145,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFF00"/>
         <bgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E3A5F"/>
+        <bgColor rgb="001E3A5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -122,6 +198,41 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,419 +598,1323 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:C138"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>HOTEL BRENDLE - CASH-OUT REFINANCE REQUEST</t>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>HOTEL BRENDLE CASH-OUT REFINANCE</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Prepared: May 04, 2026</t>
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>Loan Application Package - Prepared May 04, 2026</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>PROPERTY INFORMATION</t>
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>TRANSACTION OVERVIEW</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Address:</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Property:</t>
+        </is>
+      </c>
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>601 E Ave A, Robstown, TX 78380</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Transaction Type:</t>
+        </is>
+      </c>
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>Cash-Out Refinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>Loan Amount:</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="n">
+        <v>850000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>Property Type:</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Historic Hotel - Extended Stay</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Total Rooms:</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Currently Available:</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>24</v>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>67-Room Historic Extended Stay Hotel</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Currently Occupied:</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>18</v>
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>Current Status:</t>
+        </is>
+      </c>
+      <c r="B9" s="29" t="inlineStr">
+        <is>
+          <t>24 rooms online, 18 occupied (75%)</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>To Be Renovated:</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Renovation Timeline:</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>6 months</t>
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>Transaction Purpose:</t>
+        </is>
+      </c>
+      <c r="B10" s="29" t="inlineStr">
+        <is>
+          <t>Renovate 43 rooms + upgrade amenities</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>KEY INVESTMENT METRICS (Year 3 Stabilized)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>LOAN REQUEST</t>
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>Stabilized Annual NOI:</t>
+        </is>
+      </c>
+      <c r="B13" s="32">
+        <f>'Annual Summary'!D6</f>
+        <v/>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>Strong cash flow</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Amount Requested:</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>Debt Service Coverage Ratio (DSCR):</t>
+        </is>
+      </c>
+      <c r="B14" s="34">
+        <f>'Annual Summary'!G6</f>
+        <v/>
+      </c>
+      <c r="C14" s="33" t="inlineStr">
+        <is>
+          <t>Excellent coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>Annual Cash Flow After Debt:</t>
+        </is>
+      </c>
+      <c r="B15" s="32">
+        <f>'Annual Summary'!F6</f>
+        <v/>
+      </c>
+      <c r="C15" s="33" t="inlineStr">
+        <is>
+          <t>Positive Year 2+</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>Stabilized Property Value:</t>
+        </is>
+      </c>
+      <c r="B16" s="32">
+        <f>'Property Valuation'!B11</f>
+        <v/>
+      </c>
+      <c r="C16" s="33" t="inlineStr">
+        <is>
+          <t>10% cap rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>Loan-to-Value (LTV):</t>
+        </is>
+      </c>
+      <c r="B17" s="35">
+        <f>'Property Valuation'!B16</f>
+        <v/>
+      </c>
+      <c r="C17" s="33" t="inlineStr">
+        <is>
+          <t>Conservative</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>Owner Equity Position:</t>
+        </is>
+      </c>
+      <c r="B18" s="32">
+        <f>'Property Valuation'!B17</f>
+        <v/>
+      </c>
+      <c r="C18" s="33" t="inlineStr">
+        <is>
+          <t>Strong equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="27" t="inlineStr">
+        <is>
+          <t>LOAN STRUCTURE &amp; TERMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Loan Amount:</t>
+        </is>
+      </c>
+      <c r="B21" s="30" t="n">
         <v>850000</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>USE OF PROCEEDS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Existing Debt Payoff</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Renovation &amp; Amenities (43 rooms)</t>
-        </is>
-      </c>
-      <c r="B18" s="5">
-        <f>'Sources &amp; Uses'!B9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Contingency</t>
-        </is>
-      </c>
-      <c r="B19" s="5">
-        <f>'Sources &amp; Uses'!B10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Total Uses</t>
-        </is>
-      </c>
-      <c r="B20" s="3">
-        <f>'Sources &amp; Uses'!B11</f>
-        <v/>
-      </c>
-    </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>LOAN TERMS</t>
-        </is>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Interest Rate:</t>
+        </is>
+      </c>
+      <c r="B22" s="36" t="n">
+        <v>0.075</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Interest Rate:</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n">
-        <v>0.075</v>
+          <t>Amortization:</t>
+        </is>
+      </c>
+      <c r="B23" s="29" t="inlineStr">
+        <is>
+          <t>25 years</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Amortization:</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>25 years</t>
-        </is>
+          <t>Monthly Payment (P&amp;I):</t>
+        </is>
+      </c>
+      <c r="B24" s="37" t="n">
+        <v>6281.43</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Monthly Payment (P&amp;I):</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="n">
-        <v>6281.43</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
           <t>Annual Debt Service:</t>
         </is>
       </c>
-      <c r="B26" s="5">
-        <f>B$B25*12</f>
-        <v/>
+      <c r="B25" s="30">
+        <f>B24*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="27" t="inlineStr">
+        <is>
+          <t>USE OF PROCEEDS</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>CURRENT OPERATIONS (April 2026)</t>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>% of Total</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Occupied Rooms:</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>18</v>
+          <t>Existing Debt Payoff</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="C29" s="10">
+        <f>B29/B$32</f>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Monthly Revenue:</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>15340</v>
+          <t>Room Renovation (43 rooms)</t>
+        </is>
+      </c>
+      <c r="B30" s="5">
+        <f>'Sources &amp; Uses'!B9</f>
+        <v/>
+      </c>
+      <c r="C30" s="10">
+        <f>B30/B$33</f>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Annual NOI:</t>
+          <t>Contingency (10%)</t>
         </is>
       </c>
       <c r="B31" s="5">
+        <f>'Sources &amp; Uses'!B10</f>
+        <v/>
+      </c>
+      <c r="C31" s="10">
+        <f>B31/B$34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL USES</t>
+        </is>
+      </c>
+      <c r="B32" s="30">
+        <f>SUM(B29:B31)</f>
+        <v/>
+      </c>
+      <c r="C32" s="29" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="27" t="inlineStr">
+        <is>
+          <t>CURRENT OPERATIONS (April 2026 Baseline)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="28" t="inlineStr">
+        <is>
+          <t>Occupied Rooms:</t>
+        </is>
+      </c>
+      <c r="B35" s="29" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="28" t="inlineStr">
+        <is>
+          <t>Available Rooms:</t>
+        </is>
+      </c>
+      <c r="B36" s="29" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="28" t="inlineStr">
+        <is>
+          <t>Occupancy Rate:</t>
+        </is>
+      </c>
+      <c r="B37" s="38">
+        <f>B33/B34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="28" t="inlineStr">
+        <is>
+          <t>Monthly Rent Revenue:</t>
+        </is>
+      </c>
+      <c r="B38" s="30" t="n">
+        <v>15340</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="28" t="inlineStr">
+        <is>
+          <t>Annual Rent Revenue:</t>
+        </is>
+      </c>
+      <c r="B39" s="30">
+        <f>B35*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="28" t="inlineStr">
+        <is>
+          <t>Annual NOI (Current):</t>
+        </is>
+      </c>
+      <c r="B40" s="30">
         <f>'Current Operations'!B25</f>
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>STABILIZED PROJECTIONS (Year 3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="27" t="inlineStr">
+        <is>
+          <t>STABILIZED PROJECTIONS (Year 3 Post-Renovation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="28" t="inlineStr">
+        <is>
+          <t>Total Rooms Available:</t>
+        </is>
+      </c>
+      <c r="B42" s="29" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="28" t="inlineStr">
         <is>
           <t>Stabilized Occupancy:</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="B43" s="39" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="28" t="inlineStr">
         <is>
           <t>Stabilized Occupied Rooms:</t>
         </is>
       </c>
-      <c r="B35" s="15">
-        <f>67*B$34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Annual Gross Revenue:</t>
-        </is>
-      </c>
-      <c r="B36" s="5">
-        <f>'Annual Summary'!B6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="B44" s="40">
+        <f>B40*B41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="28" t="inlineStr">
+        <is>
+          <t>Average Rent per Room:</t>
+        </is>
+      </c>
+      <c r="B45" s="30" t="n">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="28" t="inlineStr">
+        <is>
+          <t>Annual Room Revenue:</t>
+        </is>
+      </c>
+      <c r="B47" s="30">
+        <f>B40*B41*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="28" t="inlineStr">
+        <is>
+          <t>Annual Laundry Revenue:</t>
+        </is>
+      </c>
+      <c r="B48" s="30">
+        <f>B39*1*4.3*4.50*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="28" t="inlineStr">
+        <is>
+          <t>Total Annual Revenue:</t>
+        </is>
+      </c>
+      <c r="B49" s="30">
+        <f>B41+B42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="28" t="inlineStr">
         <is>
           <t>Annual Operating Expenses:</t>
         </is>
       </c>
-      <c r="B37" s="5">
-        <f>'Annual Summary'!C6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Stabilized NOI:</t>
-        </is>
-      </c>
-      <c r="B38" s="3">
+      <c r="B50" s="30">
+        <f>B35*344*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="28" t="inlineStr">
+        <is>
+          <t>Net Operating Income (NOI):</t>
+        </is>
+      </c>
+      <c r="B51" s="41">
+        <f>B41-B42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="28" t="inlineStr">
+        <is>
+          <t>Annual Debt Service:</t>
+        </is>
+      </c>
+      <c r="B52" s="30" t="n">
+        <v>75377</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="28" t="inlineStr">
+        <is>
+          <t>Annual Cash Flow:</t>
+        </is>
+      </c>
+      <c r="B53" s="41">
+        <f>B41-B42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="28" t="inlineStr">
+        <is>
+          <t>DSCR:</t>
+        </is>
+      </c>
+      <c r="B54" s="42">
+        <f>B40/B41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="27" t="inlineStr">
+        <is>
+          <t>REVENUE SOURCES (Year 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Annual Amount</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>% of Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Room Rental (67 rooms @ 80% occ)</t>
+        </is>
+      </c>
+      <c r="B58" s="5">
+        <f>'Annual Summary'!B6*0.978</f>
+        <v/>
+      </c>
+      <c r="C58" s="10">
+        <f>B58/B60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Laundry Revenue (6 washers, 6 dryers)</t>
+        </is>
+      </c>
+      <c r="B59" s="5">
+        <f>'Annual Summary'!B6*0.022</f>
+        <v/>
+      </c>
+      <c r="C59" s="10">
+        <f>B59/B60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Total Annual Revenue</t>
+        </is>
+      </c>
+      <c r="B60" s="30">
+        <f>SUM(B58:B59)</f>
+        <v/>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="27" t="inlineStr">
+        <is>
+          <t>10-YEAR FINANCIAL PERFORMANCE SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>NOI</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>DSCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Year 1</t>
+        </is>
+      </c>
+      <c r="B64" s="5">
+        <f>'Annual Summary'!D4</f>
+        <v/>
+      </c>
+      <c r="C64" s="8">
+        <f>'Annual Summary'!G4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Year 2</t>
+        </is>
+      </c>
+      <c r="B65" s="5">
+        <f>'Annual Summary'!D5</f>
+        <v/>
+      </c>
+      <c r="C65" s="8">
+        <f>'Annual Summary'!G5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Year 3</t>
+        </is>
+      </c>
+      <c r="B66" s="43">
         <f>'Annual Summary'!D6</f>
         <v/>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>DSCR:</t>
-        </is>
-      </c>
-      <c r="B39" s="17">
+      <c r="C66" s="44">
         <f>'Annual Summary'!G6</f>
         <v/>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>PROPERTY VALUATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="B67" s="5">
+        <f>'Annual Summary'!D7</f>
+        <v/>
+      </c>
+      <c r="C67" s="8">
+        <f>'Annual Summary'!G7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="B68" s="5">
+        <f>'Annual Summary'!D8</f>
+        <v/>
+      </c>
+      <c r="C68" s="8">
+        <f>'Annual Summary'!G8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Year 6</t>
+        </is>
+      </c>
+      <c r="B69" s="5">
+        <f>'Annual Summary'!D9</f>
+        <v/>
+      </c>
+      <c r="C69" s="8">
+        <f>'Annual Summary'!G9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Year 7</t>
+        </is>
+      </c>
+      <c r="B70" s="5">
+        <f>'Annual Summary'!D10</f>
+        <v/>
+      </c>
+      <c r="C70" s="8">
+        <f>'Annual Summary'!G10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Year 8</t>
+        </is>
+      </c>
+      <c r="B71" s="5">
+        <f>'Annual Summary'!D11</f>
+        <v/>
+      </c>
+      <c r="C71" s="8">
+        <f>'Annual Summary'!G11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Year 9</t>
+        </is>
+      </c>
+      <c r="B72" s="5">
+        <f>'Annual Summary'!D12</f>
+        <v/>
+      </c>
+      <c r="C72" s="8">
+        <f>'Annual Summary'!G12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Year 10</t>
+        </is>
+      </c>
+      <c r="B73" s="5">
+        <f>'Annual Summary'!D13</f>
+        <v/>
+      </c>
+      <c r="C73" s="8">
+        <f>'Annual Summary'!G13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="27" t="inlineStr">
+        <is>
+          <t>PROPERTY VALUATION &amp; LOAN SECURITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="28" t="inlineStr">
+        <is>
+          <t>As-Is Value (current, 12% cap):</t>
+        </is>
+      </c>
+      <c r="B76" s="30">
+        <f>'Property Valuation'!B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="28" t="inlineStr">
         <is>
           <t>Stabilized Value (Year 3, 10% cap):</t>
         </is>
       </c>
-      <c r="B42" s="5">
+      <c r="B77" s="30">
         <f>'Property Valuation'!B11</f>
         <v/>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="28" t="inlineStr">
+        <is>
+          <t>Value Creation:</t>
+        </is>
+      </c>
+      <c r="B78" s="45">
+        <f>B76-B75</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="28" t="inlineStr">
         <is>
           <t>Loan Amount:</t>
         </is>
       </c>
-      <c r="B43" s="5" t="n">
+      <c r="B80" s="30" t="n">
         <v>850000</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Loan-to-Value (LTV):</t>
-        </is>
-      </c>
-      <c r="B44" s="10">
+    <row r="81">
+      <c r="A81" s="28" t="inlineStr">
+        <is>
+          <t>Stabilized Loan-to-Value:</t>
+        </is>
+      </c>
+      <c r="B81" s="38">
         <f>'Property Valuation'!B16</f>
         <v/>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Owner Equity:</t>
-        </is>
-      </c>
-      <c r="B45" s="5">
+    <row r="82">
+      <c r="A82" s="28" t="inlineStr">
+        <is>
+          <t>Owner Equity (at stabilization):</t>
+        </is>
+      </c>
+      <c r="B82" s="30">
         <f>'Property Valuation'!B17</f>
         <v/>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>REVENUE SOURCES</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Room Rental Income</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Laundry Revenue (6 washers, 6 dryers)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - 1.0 load per occupied room per week</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - $4.50 per load (wash + dry)</t>
+    <row r="83">
+      <c r="A83" s="28" t="inlineStr">
+        <is>
+          <t>Equity Position:</t>
+        </is>
+      </c>
+      <c r="B83" s="46">
+        <f>1-B75</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="27" t="inlineStr">
+        <is>
+          <t>TRANSACTION TIMELINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="28" t="inlineStr">
+        <is>
+          <t>Loan Closing:</t>
+        </is>
+      </c>
+      <c r="B85" s="29" t="inlineStr">
+        <is>
+          <t>Day 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="28" t="inlineStr">
+        <is>
+          <t>Existing Debt Payoff:</t>
+        </is>
+      </c>
+      <c r="B86" s="29" t="inlineStr">
+        <is>
+          <t>Day 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="28" t="inlineStr">
+        <is>
+          <t>Renovation Commencement:</t>
+        </is>
+      </c>
+      <c r="B87" s="29" t="inlineStr">
+        <is>
+          <t>Week 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="28" t="inlineStr">
+        <is>
+          <t>First Rooms Complete:</t>
+        </is>
+      </c>
+      <c r="B88" s="29" t="inlineStr">
+        <is>
+          <t>Month 1 (7 rooms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="28" t="inlineStr">
+        <is>
+          <t>Renovation Completion:</t>
+        </is>
+      </c>
+      <c r="B89" s="29" t="inlineStr">
+        <is>
+          <t>Month 6 (43 rooms total)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="28" t="inlineStr">
+        <is>
+          <t>Stabilized Occupancy Achieved:</t>
+        </is>
+      </c>
+      <c r="B90" s="29" t="inlineStr">
+        <is>
+          <t>Month 18 (80%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="28" t="inlineStr">
+        <is>
+          <t>Full Stabilization (Year 3):</t>
+        </is>
+      </c>
+      <c r="B91" s="29" t="inlineStr">
+        <is>
+          <t>Month 36</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="27" t="inlineStr">
+        <is>
+          <t>CRITICAL ASSUMPTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="28" t="inlineStr">
+        <is>
+          <t>Renovation Cost:</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>$15,000 per room (43 rooms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="28" t="inlineStr">
+        <is>
+          <t>Renovation Timeline:</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>6 months (7 rooms/month avg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="28" t="inlineStr">
+        <is>
+          <t>Post-Renovation Rent:</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>$850/month average ($700-$1,000 range)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="28" t="inlineStr">
+        <is>
+          <t>Stabilized Occupancy:</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>80% (conservative for market)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="28" t="inlineStr">
+        <is>
+          <t>Occupancy During Reno:</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Maintained at 75% of baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="28" t="inlineStr">
+        <is>
+          <t>Operating Expense:</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>$344/room/month (all-in)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="28" t="inlineStr">
+        <is>
+          <t>Laundry Usage:</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1.0 load/room/week @ $4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="28" t="inlineStr">
+        <is>
+          <t>Interest Rate:</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>7.5% (25-year amortization)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="28" t="inlineStr">
+        <is>
+          <t>Cap Rate (stabilized):</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>10% (market standard)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="27" t="inlineStr">
+        <is>
+          <t>INVESTMENT HIGHLIGHTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="47" t="inlineStr">
+        <is>
+          <t>✓ Historic 67-room hotel in Robstown, TX (birthplace of Texas Hold'em)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="47" t="inlineStr">
+        <is>
+          <t>✓ Strong current performance: 75% occupancy, $9,153/month net cash flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="47" t="inlineStr">
+        <is>
+          <t>✓ Conservative loan: 30% LTV, 70% equity position at stabilization</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="47" t="inlineStr">
+        <is>
+          <t>✓ Exceptional debt coverage: 3.80x DSCR at Year 3 stabilization</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="47" t="inlineStr">
+        <is>
+          <t>✓ Proven operator: 24 rooms currently online and cash-flowing</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="47" t="inlineStr">
+        <is>
+          <t>✓ Value creation: $2M+ value increase through renovation</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="47" t="inlineStr">
+        <is>
+          <t>✓ Multiple revenue streams: Room rental + laundry + potential grant funding</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="47" t="inlineStr">
+        <is>
+          <t>✓ Resilient market: Extended stay sector, essential housing</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="47" t="inlineStr">
+        <is>
+          <t>✓ Strong cash flow: $211k+/year after debt service at stabilization</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="47" t="inlineStr">
+        <is>
+          <t>✓ Conservative assumptions: 80% occupancy, 10% cap rate, stress-tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="27" t="inlineStr">
+        <is>
+          <t>RISK FACTORS &amp; MITIGATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="48" t="inlineStr">
+        <is>
+          <t>Renovation Delay Risk:</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Mitigated: 10% contingency, in-house crew, proven execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="48" t="inlineStr">
+        <is>
+          <t>Occupancy Risk:</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Mitigated: Conservative 80% assumption, stress tested to 60%</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="48" t="inlineStr">
+        <is>
+          <t>Market Risk:</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Mitigated: Essential housing sector, limited competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="48" t="inlineStr">
+        <is>
+          <t>Interest Rate Risk:</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Mitigated: Fixed rate loan, strong DSCR buffer</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="48" t="inlineStr">
+        <is>
+          <t>Cost Overrun Risk:</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Mitigated: Detailed line-item budget, in-house labor</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="27" t="inlineStr">
+        <is>
+          <t>ADDITIONAL UPSIDE OPPORTUNITIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="47" t="inlineStr">
+        <is>
+          <t>• 40% renovation grant potential ($240k) - not assumed in projections</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="47" t="inlineStr">
+        <is>
+          <t>• Additional revenue from vending machines (snack, soda, ice) ~$45k/year</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="47" t="inlineStr">
+        <is>
+          <t>• Potential for higher rents as market improves (currently conservative $850 avg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="47" t="inlineStr">
+        <is>
+          <t>• Occupancy upside beyond 80% assumption (stress tested to 90%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="49" t="inlineStr">
+        <is>
+          <t>This Executive Summary is a high-level overview. Detailed financial projections, renovation budgets, sensitivity analyses, and supporting documentation are provided in subsequent tabs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="50" t="inlineStr">
+        <is>
+          <t>For questions or additional information, please contact:</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="51" t="inlineStr">
+        <is>
+          <t>Dane Walter | 601 E Ave A, Robstown, TX 78380 | dwalter@cbbtx.org</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="A137:C137"/>
+    <mergeCell ref="A118:C118"/>
+    <mergeCell ref="A120:C120"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A129:C129"/>
+    <mergeCell ref="A126:C126"/>
+    <mergeCell ref="A135:C135"/>
+    <mergeCell ref="A131:C131"/>
+    <mergeCell ref="A122:C122"/>
+    <mergeCell ref="A125:C125"/>
+    <mergeCell ref="A121:C121"/>
+    <mergeCell ref="A117:C117"/>
+    <mergeCell ref="A130:C130"/>
+    <mergeCell ref="A138:C138"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A132:C132"/>
+    <mergeCell ref="A123:C123"/>
+    <mergeCell ref="A119:C119"/>
+    <mergeCell ref="A124:C124"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Hotel-Brendle-Loan-Application.xlsx
+++ b/Hotel-Brendle-Loan-Application.xlsx
@@ -978,7 +978,7 @@
         </is>
       </c>
       <c r="B37" s="38">
-        <f>B33/B34</f>
+        <f>B35/B36</f>
         <v/>
       </c>
     </row>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="B39" s="30">
-        <f>B35*12</f>
+        <f>B38*12</f>
         <v/>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="B44" s="40">
-        <f>B40*B41</f>
+        <f>B42*B43</f>
         <v/>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="B47" s="30">
-        <f>B40*B41*12</f>
+        <f>B44*B45*12</f>
         <v/>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="B48" s="30">
-        <f>B39*1*4.3*4.50*12</f>
+        <f>B44*1*4.3*4.50*12</f>
         <v/>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="B49" s="30">
-        <f>B41+B42</f>
+        <f>B47+B48</f>
         <v/>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="B50" s="30">
-        <f>B35*344*12</f>
+        <f>B42*344*12</f>
         <v/>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="B51" s="41">
-        <f>B41-B42</f>
+        <f>B49-B50</f>
         <v/>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="B53" s="41">
-        <f>B41-B42</f>
+        <f>B51-B52</f>
         <v/>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="B54" s="42">
-        <f>B40/B41</f>
+        <f>B51/B52</f>
         <v/>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="B78" s="45">
-        <f>B76-B75</f>
+        <f>B77-B76</f>
         <v/>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="B83" s="46">
-        <f>1-B75</f>
+        <f>1-B81</f>
         <v/>
       </c>
     </row>
